--- a/行事曆/2027行事曆_華嚴海會更新版.xlsx
+++ b/行事曆/2027行事曆_華嚴海會更新版.xlsx
@@ -17,8 +17,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'活動總表'!$20:$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'活動總表'!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'活動重疊檢查'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'活動重疊檢查'!$A$1:$D$99</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'更新說明'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'活動重疊檢查'!$A$1:$D$87</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'更新說明'!$A$1:$B$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -235,9 +235,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -630,7 +627,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>每日顯示農曆日期；本版更新：華嚴海會 2027/12/11–2027/12/22，共 12 天。活動重疊與安排確認請見「活動重疊檢查」頁。</t>
+          <t>每日顯示農曆日期；本版更新：華嚴海會 2027/12/11–2027/12/22，共 12 天；該期間原排定之其他活動均已取消。</t>
         </is>
       </c>
     </row>
@@ -3478,95 +3475,77 @@
       <c r="G98" s="7" t="inlineStr">
         <is>
           <t>11（農11/14）
-華嚴海會
-秋季班
-好好讀楞嚴（善覺）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="73.5" customHeight="1">
+華嚴海會</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="34" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
           <t>12（農11/15）
-華嚴海會
-秋季班
-兒童哲學班（秋季）
-企業專班：台中</t>
+華嚴海會</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>13（農11/16）
-華嚴海會
-秋季班</t>
+華嚴海會</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
           <t>14（農11/17）
-華嚴海會
-秋季班</t>
+華嚴海會</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
           <t>15（農11/18）
-華嚴海會
-秋季班</t>
+華嚴海會</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
           <t>16（農11/19）
-華嚴海會
-秋季班</t>
+華嚴海會</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
           <t>17（農11/20）
-華嚴海會
-秋季班</t>
+華嚴海會</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
           <t>18（農11/21）
-華嚴海會
-秋季班
-一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="73.5" customHeight="1">
+華嚴海會</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="34" customHeight="1">
       <c r="A100" s="7" t="inlineStr">
         <is>
           <t>19（農11/22）
-華嚴海會
-秋季班
-兒童哲學班（秋季）
-楞嚴經（新加坡）</t>
+華嚴海會</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
           <t>20（農11/23）
-華嚴海會
-秋季班</t>
+華嚴海會</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
           <t>21（農11/24）
-華嚴海會
-秋季班</t>
+華嚴海會</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
           <t>22（農11/25）
-華嚴海會
-秋季班</t>
+華嚴海會</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3730,12 +3709,12 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>共 14 堂</t>
+          <t>共 12 堂</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>2027/9/26、2027/10/3、2027/10/10、2027/10/17、2027/10/24、2027/10/31、2027/11/7、2027/11/14、2027/11/21、2027/11/28、2027/12/5、2027/12/12、2027/12/19、2027/12/26</t>
+          <t>2027/9/26、2027/10/3、2027/10/10、2027/10/17、2027/10/24、2027/10/31、2027/11/7、2027/11/14、2027/11/21、2027/11/28、2027/12/5、2027/12/26（原 14 堂，12/12、12/19 因華嚴海會取消）</t>
         </is>
       </c>
       <c r="D6" s="11" t="n"/>
@@ -3798,7 +3777,7 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>2027/9/13–2027/12/24（週一至週五晚上）</t>
+          <t>2027/9/13–2027/12/24（週一至週五晚上）；12/11–12/22 華嚴海會期間停課，實際上課 9/13–12/10、12/23–12/24</t>
         </is>
       </c>
       <c r="D9" s="11" t="n"/>
@@ -3856,12 +3835,12 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>共 8 堂</t>
+          <t>共 7 堂</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/8/8、2027/10/10、2027/11/14、2027/12/12</t>
+          <t>2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/8/8、2027/10/10、2027/11/14（原 8 堂，12/12 因華嚴海會取消）</t>
         </is>
       </c>
       <c r="D12" s="11" t="n"/>
@@ -3877,12 +3856,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>共 7 堂</t>
+          <t>共 6 堂</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/10/9、2027/11/13、2027/12/11</t>
+          <t>2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/10/9、2027/11/13（原 7 堂，12/11 因華嚴海會取消）</t>
         </is>
       </c>
       <c r="D13" s="11" t="n"/>
@@ -3940,12 +3919,12 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>共 8 堂</t>
+          <t>共 7 堂</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>2027/3/20、2027/4/17、2027/5/15、2027/7/17、2027/9/18、2027/10/16、2027/11/20、2027/12/18</t>
+          <t>2027/3/20、2027/4/17、2027/5/15、2027/7/17、2027/9/18、2027/10/16、2027/11/20（原 8 堂，12/18 因華嚴海會取消）</t>
         </is>
       </c>
       <c r="D16" s="11" t="n"/>
@@ -3961,12 +3940,12 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>共 8 堂</t>
+          <t>共 7 堂</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>2027/3/21、2027/4/18、2027/5/16、2027/7/18、2027/9/19、2027/10/17、2027/11/21、2027/12/19</t>
+          <t>2027/3/21、2027/4/18、2027/5/16、2027/7/18、2027/9/19、2027/10/17、2027/11/21（原 8 堂，12/19 因華嚴海會取消）</t>
         </is>
       </c>
       <c r="D17" s="11" t="n"/>
@@ -4635,7 +4614,7 @@
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2027/9/13–2027/12/24</t>
+          <t>2027/9/13–2027/12/24（12/11–12/22 停課）</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -4665,7 +4644,7 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>共 15 週</t>
+          <t>原共 15 週；華嚴海會期間（12/11–12/22）停課，實際上課 9/13–12/10、12/23–12/24</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4718,7 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>共 12 天（本次更新；原「歲末大型華嚴法會」2027/12/25–2028/1/2 調整為本案）</t>
+          <t>共 12 天（本次更新）；原「歲末大型華嚴法會」2027/12/25–2028/1/2 調整為本案；本期間為重大活動，原有之其他活動均已取消</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4792,7 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>共 14 堂；日期詳見上方課程場次表</t>
+          <t>共 12 堂（原 14 堂；12/12、12/19 因華嚴海會取消）；日期詳見上方課程場次表</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5095,7 @@
     <row r="52" ht="46" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>2027/1/10、2027/2/14、2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/8、2027/9/12、2027/10/10、2027/11/14、2027/12/12</t>
+          <t>2027/1/10、2027/2/14、2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/8、2027/9/12、2027/10/10、2027/11/14</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -5146,14 +5125,14 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>每月第二個星期日</t>
+          <t>每月第二個星期日；12/12 因華嚴海會取消</t>
         </is>
       </c>
     </row>
     <row r="53" ht="46" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2027/1/9、2027/2/13、2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/7/10、2027/8/14、2027/9/11、2027/10/9、2027/11/13、2027/12/11</t>
+          <t>2027/1/9、2027/2/13、2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/7/10、2027/8/14、2027/9/11、2027/10/9、2027/11/13</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -5183,7 +5162,7 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>每月第二週週六</t>
+          <t>每月第二週週六；12/11 因華嚴海會取消</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5235,7 +5214,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>列出同一日安排 2 項（含）以上活動之日期；華嚴海會（12/11–12/22）期間以紅底標示。</t>
+          <t>列出同一日安排 2 項（含）以上活動之日期。華嚴海會（12/11–12/22）期間之衝突活動已全數取消，故該期間不再出現於本表。</t>
         </is>
       </c>
     </row>
@@ -6918,246 +6897,6 @@
       <c r="D87" s="6" t="inlineStr">
         <is>
           <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/11</t>
-        </is>
-      </c>
-      <c r="B88" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C88" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>華嚴海會、秋季班、好好讀楞嚴（善覺）</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/12</t>
-        </is>
-      </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C89" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>華嚴海會、秋季班、兒童哲學班（秋季）、企業專班：台中</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/13</t>
-        </is>
-      </c>
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>星期一</t>
-        </is>
-      </c>
-      <c r="C90" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>華嚴海會、秋季班</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/14</t>
-        </is>
-      </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>星期二</t>
-        </is>
-      </c>
-      <c r="C91" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>華嚴海會、秋季班</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/15</t>
-        </is>
-      </c>
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>星期三</t>
-        </is>
-      </c>
-      <c r="C92" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>華嚴海會、秋季班</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/16</t>
-        </is>
-      </c>
-      <c r="B93" s="17" t="inlineStr">
-        <is>
-          <t>星期四</t>
-        </is>
-      </c>
-      <c r="C93" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>華嚴海會、秋季班</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/17</t>
-        </is>
-      </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>星期五</t>
-        </is>
-      </c>
-      <c r="C94" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>華嚴海會、秋季班</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/18</t>
-        </is>
-      </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C95" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>華嚴海會、秋季班、一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/19</t>
-        </is>
-      </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C96" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>華嚴海會、秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/20</t>
-        </is>
-      </c>
-      <c r="B97" s="17" t="inlineStr">
-        <is>
-          <t>星期一</t>
-        </is>
-      </c>
-      <c r="C97" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>華嚴海會、秋季班</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/21</t>
-        </is>
-      </c>
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>星期二</t>
-        </is>
-      </c>
-      <c r="C98" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>華嚴海會、秋季班</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/22</t>
-        </is>
-      </c>
-      <c r="B99" s="17" t="inlineStr">
-        <is>
-          <t>星期三</t>
-        </is>
-      </c>
-      <c r="C99" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>華嚴海會、秋季班</t>
         </is>
       </c>
     </row>
@@ -7177,7 +6916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7192,7 +6931,7 @@
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>更新項目</t>
         </is>
@@ -7204,7 +6943,7 @@
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>期間</t>
         </is>
@@ -7216,7 +6955,7 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>天數</t>
         </is>
@@ -7228,7 +6967,7 @@
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>原排程</t>
         </is>
@@ -7240,9 +6979,9 @@
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>異動內容</t>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>異動內容 1</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -7252,36 +6991,65 @@
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>同期並行活動</t>
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>異動內容 2</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>秋季班（12/11–12/22 每日）、好好讀楞嚴（善覺）12/11、兒童哲學班（秋季）12/12・12/19、企業專班：台中 12/12、一日禪（新加坡）12/18、楞嚴經（新加坡）12/19</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+          <t>華嚴海會為重大活動，2027/12/11–12/22 期間原排定之所有活動全數取消，該 12 天僅保留華嚴海會。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="92" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>取消活動明細</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>秋季班：12/11、12/12、12/13、12/14、12/15、12/16、12/17、12/18、12/19、12/20、12/21、12/22（共 12 場／日）
+好好讀楞嚴（善覺）：12/11（共 1 場／日）
+兒童哲學班（秋季）：12/12、12/19（共 2 場／日）
+企業專班：台中：12/12（共 1 場／日）
+一日禪（新加坡）：12/18（共 1 場／日）
+楞嚴經（新加坡）：12/19（共 1 場／日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>連帶調整</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>兒童哲學班（秋季）14 堂→12 堂；企業專班：台中 8 堂→7 堂；好好讀楞嚴：板橋 7 堂→6 堂；一日禪（新加坡）8 堂→7 堂；楞嚴經（新加坡）8 堂→7 堂；秋季班原 9/13–12/24 共 15 週，12/11–12/22 停課，實際上課 9/13–12/10、12/23–12/24。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>其他說明</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>除上述華嚴海會異動外，其餘月份與活動內容均與原 2027 行事曆相同。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>除上述異動外，其餘月份與活動內容均與原 2027 行事曆相同。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>製作日期</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>2026/10/05</t>
         </is>

--- a/行事曆/2027行事曆_華嚴海會更新版.xlsx
+++ b/行事曆/2027行事曆_華嚴海會更新版.xlsx
@@ -15,10 +15,10 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'2027行事曆'!$A$1:$G$102</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'活動總表'!$20:$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'活動總表'!$A$1:$G$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'活動總表'!$A$1:$G$54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'活動重疊檢查'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'活動重疊檢查'!$A$1:$D$87</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'更新說明'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'活動重疊檢查'!$A$1:$D$89</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'更新說明'!$A$1:$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +66,12 @@
     <font>
       <name val="Microsoft JhengHei"/>
       <b val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
       <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
@@ -88,7 +94,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -108,6 +114,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -214,10 +225,13 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -225,13 +239,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -627,7 +641,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>每日顯示農曆日期；本版更新：華嚴海會 2027/12/11–2027/12/22，共 12 天；該期間原排定之其他活動均已取消。</t>
+          <t>每日顯示農曆日期；本版更新：華嚴海會 2027/12/15–2027/12/26（共 12 天），前置作業 2027/12/13–2027/12/14（共 2 天）；該期間原排定之其他活動均已取消。</t>
         </is>
       </c>
     </row>
@@ -3472,51 +3486,54 @@
 秋季班</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr">
+      <c r="G98" s="6" t="inlineStr">
         <is>
           <t>11（農11/14）
-華嚴海會</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="34" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
+秋季班
+好好讀楞嚴（善覺）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>12（農11/15）
-華嚴海會</t>
+秋季班
+兒童哲學班（秋季）
+企業專班：台中</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>13（農11/16）
-華嚴海會</t>
+華嚴海會前置作業</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
           <t>14（農11/17）
-華嚴海會</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="inlineStr">
+華嚴海會前置作業</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>15（農11/18）
 華嚴海會</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="E99" s="8" t="inlineStr">
         <is>
           <t>16（農11/19）
 華嚴海會</t>
         </is>
       </c>
-      <c r="F99" s="7" t="inlineStr">
+      <c r="F99" s="8" t="inlineStr">
         <is>
           <t>17（農11/20）
 華嚴海會</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr">
+      <c r="G99" s="8" t="inlineStr">
         <is>
           <t>18（農11/21）
 華嚴海會</t>
@@ -3524,53 +3541,54 @@
       </c>
     </row>
     <row r="100" ht="34" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>19（農11/22）
 華嚴海會</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>20（農11/23）
 華嚴海會</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>21（農11/24）
 華嚴海會</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>22（農11/25）
 華嚴海會</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>23（農11/26）
-秋季班</t>
-        </is>
-      </c>
-      <c r="F100" s="6" t="inlineStr">
+華嚴海會</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>24（農11/27）
-秋季班</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>25（農11/28）</t>
+華嚴海會</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>25（農11/28）
+華嚴海會</t>
         </is>
       </c>
     </row>
     <row r="101" ht="34" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t>26（農11/29）
-兒童哲學班（秋季）</t>
+華嚴海會</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -3633,7 +3651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3646,352 +3664,352 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>2027 年活動總表（更新版）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>一、課程場次</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>課程</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>堂數／週數</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="13" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>兒童哲學班（春季）</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>共 16 堂</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>2027/3/7、2027/3/14、2027/3/21、2027/3/28、2027/4/4、2027/4/11、2027/4/18、2027/4/25、2027/5/2、2027/5/9、2027/5/16、2027/5/23、2027/5/30、2027/6/6、2027/6/13、2027/6/20</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="13" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>兒童哲學班（秋季）</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>共 12 堂</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>2027/9/26、2027/10/3、2027/10/10、2027/10/17、2027/10/24、2027/10/31、2027/11/7、2027/11/14、2027/11/21、2027/11/28、2027/12/5、2027/12/26（原 14 堂，12/12、12/19 因華嚴海會取消）</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="12" t="n"/>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>2027/9/26、2027/10/3、2027/10/10、2027/10/17、2027/10/24、2027/10/31、2027/11/7、2027/11/14、2027/11/21、2027/11/28、2027/12/5、2027/12/12（原 14 堂，12/19、12/26 因華嚴海會取消）</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="13" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>春季班</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>共 17 週</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>2027/3/2–2027/6/18（週一至週五晚上，首週自週二起）</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>暑期班</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>共 5 週</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>2027/7/12–2027/8/13（週一至週五晚上）</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="13" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>秋季班</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>共 15 週</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>2027/9/13–2027/12/24（週一至週五晚上）；12/11–12/22 華嚴海會期間停課，實際上課 9/13–12/10、12/23–12/24</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>原共 15 週</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>2027/9/13–2027/12/24（週一至週五晚上）；12/13 起因華嚴海會停課，實際上課 2027/9/13–2027/12/10，共 13 週</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="13" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>企業專班：台北</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>共 8 堂</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/8/7、2027/10/2、2027/11/6、2027/12/4</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="13" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>企業專班：高雄</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>共 8 堂</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/10/3、2027/11/7、2027/12/5</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="13" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>企業專班：台中</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>共 8 堂</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/8/8、2027/10/10、2027/11/14、2027/12/12</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>共 7 堂</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/8/8、2027/10/10、2027/11/14（原 8 堂，12/12 因華嚴海會取消）</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="12" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>好好讀楞嚴：板橋</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>共 6 堂</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/10/9、2027/11/13（原 7 堂，12/11 因華嚴海會取消）</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="12" t="n"/>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/10/9、2027/11/13、2027/12/11</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="13" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>英文一日禪（新加坡）</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>共 8 堂</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>2027/3/13、2027/4/3、2027/5/1、2027/6/5、2027/8/7、2027/10/2、2027/11/6、2027/12/4</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="13" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>英文楞嚴經（新加坡）</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>共 8 堂</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>2027/3/14、2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/10/3、2027/11/7、2027/12/5</t>
         </is>
       </c>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="13" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>一日禪（新加坡）</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>共 7 堂</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>2027/3/20、2027/4/17、2027/5/15、2027/7/17、2027/9/18、2027/10/16、2027/11/20（原 8 堂，12/18 因華嚴海會取消）</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="13" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>楞嚴經（新加坡）</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>共 7 堂</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>2027/3/21、2027/4/18、2027/5/16、2027/7/18、2027/9/19、2027/10/17、2027/11/21（原 8 堂，12/19 因華嚴海會取消）</t>
         </is>
       </c>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>二、活動明細</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>日期／期間</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>類別</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>地點</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -4614,7 +4632,8 @@
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2027/9/13–2027/12/24（12/11–12/22 停課）</t>
+          <t>2027/9/13–2027/12/10
+（原排至 12/24）</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -4644,7 +4663,7 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>原共 15 週；華嚴海會期間（12/11–12/22）停課，實際上課 9/13–12/10、12/23–12/24</t>
+          <t>原共 15 週；12/13 起因華嚴海會前置作業及法會停課，實際上課 9/13–12/10，共 13 週</t>
         </is>
       </c>
     </row>
@@ -4686,83 +4705,83 @@
       </c>
     </row>
     <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>2027/12/11–2027/12/22</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>星期六～星期三</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>2027/12/13–2027/12/14</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>星期一～星期二</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>華嚴海會前置作業</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>法會／大型活動</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>各分院</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>共 2 天；華嚴海會前置準備，不排其他活動</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>2027/12/15–2027/12/26</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>星期三～星期日</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>華嚴海會</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>法會／大型活動</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>待確認</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>各分院</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>共 12 天（本次更新）；原「歲末大型華嚴法會」2027/12/25–2028/1/2 調整為本案；本期間為重大活動，原有之其他活動均已取消</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>2027/3/7 起每週日</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>每週日</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>兒童哲學班（春季）</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>兒童教育</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>待確認</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>各分院</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>共 16 堂；日期詳見上方課程場次表</t>
         </is>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2027/9/26 起每週日</t>
+          <t>2027/3/7 起每週日</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -4772,7 +4791,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>兒童哲學班（秋季）</t>
+          <t>兒童哲學班（春季）</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -4792,24 +4811,24 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>共 12 堂（原 14 堂；12/12、12/19 因華嚴海會取消）；日期詳見上方課程場次表</t>
+          <t>共 16 堂；日期詳見上方課程場次表</t>
         </is>
       </c>
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2027/7/11–2027/7/17</t>
+          <t>2027/9/26 起每週日</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>星期日～星期六</t>
+          <t>每週日</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第1梯</t>
+          <t>兒童哲學班（秋季）</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -4829,14 +4848,14 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>第 1 梯次</t>
+          <t>共 12 堂（原 14 堂；12/19、12/26 因華嚴海會取消）；日期詳見上方課程場次表</t>
         </is>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2027/7/18–2027/7/24</t>
+          <t>2027/7/11–2027/7/17</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -4846,7 +4865,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第2梯</t>
+          <t>兒童夏令營 第1梯</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -4866,14 +4885,14 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>第 2 梯次</t>
+          <t>第 1 梯次</t>
         </is>
       </c>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2027/7/25–2027/7/31</t>
+          <t>2027/7/18–2027/7/24</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -4883,7 +4902,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第3梯</t>
+          <t>兒童夏令營 第2梯</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -4903,14 +4922,14 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>第 3 梯次</t>
+          <t>第 2 梯次</t>
         </is>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2027/8/1–2027/8/7</t>
+          <t>2027/7/25–2027/7/31</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -4920,7 +4939,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第4梯</t>
+          <t>兒童夏令營 第3梯</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -4940,14 +4959,14 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>第 4 梯次</t>
+          <t>第 3 梯次</t>
         </is>
       </c>
     </row>
     <row r="48" ht="34" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>2027/8/8–2027/8/14</t>
+          <t>2027/8/1–2027/8/7</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -4957,7 +4976,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第5梯</t>
+          <t>兒童夏令營 第4梯</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -4977,88 +4996,88 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>第 5 梯次</t>
+          <t>第 4 梯次</t>
         </is>
       </c>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
+          <t>2027/8/8–2027/8/14</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>星期日～星期六</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>兒童夏令營 第5梯</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>兒童教育</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>各分院</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>第 5 梯次</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
           <t>2027/8/15–2027/8/20</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>星期日～星期五</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>兒童夏令營 第6梯</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>兒童教育</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>待確認</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>各分院</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>第 6 梯次</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="46" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>2027/1/2、2027/2/6、2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/7/3、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>依各列日期</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台北</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>企業專班</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>待確認</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>善首講堂</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>每月第一個星期六</t>
         </is>
       </c>
     </row>
     <row r="51" ht="46" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>2027/1/3、2027/2/7、2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/7/4、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5</t>
+          <t>2027/1/2、2027/2/6、2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/7/3、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -5068,7 +5087,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>企業專班：台北</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -5083,19 +5102,19 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善首講堂</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>每月第一個星期日</t>
+          <t>每月第一個星期六</t>
         </is>
       </c>
     </row>
     <row r="52" ht="46" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>2027/1/10、2027/2/14、2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/8、2027/9/12、2027/10/10、2027/11/14</t>
+          <t>2027/1/3、2027/2/7、2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/7/4、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -5105,7 +5124,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -5120,19 +5139,19 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>每月第二個星期日；12/12 因華嚴海會取消</t>
+          <t>每月第一個星期日</t>
         </is>
       </c>
     </row>
     <row r="53" ht="46" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2027/1/9、2027/2/13、2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/7/10、2027/8/14、2027/9/11、2027/10/9、2027/11/13</t>
+          <t>2027/1/10、2027/2/14、2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/8、2027/9/12、2027/10/10、2027/11/14、2027/12/12</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -5142,27 +5161,64 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>企業專班</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>每月第二個星期日</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="46" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2027/1/9、2027/2/13、2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/7/10、2027/8/14、2027/9/11、2027/10/9、2027/11/13、2027/12/11</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>依各列日期</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
           <t>好好讀楞嚴（善覺）</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>一般課程</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>待確認</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>善覺講堂</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>每月第二週週六；12/11 因華嚴海會取消</t>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>每月第二週週六</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5205,7 +5261,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>2027 年活動重疊檢查</t>
         </is>
@@ -5214,44 +5270,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>列出同一日安排 2 項（含）以上活動之日期。華嚴海會（12/11–12/22）期間之衝突活動已全數取消，故該期間不再出現於本表。</t>
+          <t>列出同一日安排 2 項（含）以上活動之日期。華嚴海會前置作業及法會期間（12/13–12/26）之衝突活動已全數取消，故該期間不再出現於本表。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>活動數</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>活動內容</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>2027/3/7</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -5261,17 +5317,17 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>2027/3/13</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -5281,17 +5337,17 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>2027/3/14</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -5301,17 +5357,17 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>2027/3/15</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>星期一</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -5321,17 +5377,17 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>2027/3/16</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>星期二</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -5341,17 +5397,17 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>2027/3/17</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>星期三</t>
         </is>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -5361,17 +5417,17 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>2027/3/18</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>星期四</t>
         </is>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -5381,17 +5437,17 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>2027/3/19</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>星期五</t>
         </is>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -5401,17 +5457,17 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>2027/3/20</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -5421,17 +5477,17 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>2027/3/21</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -5441,17 +5497,17 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>2027/4/3</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -5461,17 +5517,17 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>2027/4/4</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -5481,17 +5537,17 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>2027/4/10</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -5501,17 +5557,17 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>2027/4/11</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -5521,17 +5577,17 @@
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>2027/4/18</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -5541,17 +5597,17 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>2027/5/1</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -5561,17 +5617,17 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>2027/5/2</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -5581,17 +5637,17 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>2027/5/8</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -5601,17 +5657,17 @@
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>2027/5/9</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -5621,17 +5677,17 @@
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>2027/5/10</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>星期一</t>
         </is>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -5641,17 +5697,17 @@
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>2027/5/11</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>星期二</t>
         </is>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -5661,17 +5717,17 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>2027/5/12</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>星期三</t>
         </is>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -5681,17 +5737,17 @@
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>2027/5/13</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>星期四</t>
         </is>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -5701,17 +5757,17 @@
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>2027/5/14</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>星期五</t>
         </is>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -5721,17 +5777,17 @@
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>2027/5/15</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -5741,17 +5797,17 @@
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>2027/5/16</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -5761,17 +5817,17 @@
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>2027/6/5</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -5781,17 +5837,17 @@
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>2027/6/6</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -5801,17 +5857,17 @@
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>2027/6/13</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -5821,17 +5877,17 @@
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>2027/7/12</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>星期一</t>
         </is>
       </c>
-      <c r="C34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -5841,17 +5897,17 @@
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>2027/7/13</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>星期二</t>
         </is>
       </c>
-      <c r="C35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -5861,17 +5917,17 @@
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>2027/7/14</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>星期三</t>
         </is>
       </c>
-      <c r="C36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -5881,17 +5937,17 @@
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>2027/7/15</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>星期四</t>
         </is>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -5901,17 +5957,17 @@
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>2027/7/16</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>星期五</t>
         </is>
       </c>
-      <c r="C38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -5921,17 +5977,17 @@
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>2027/7/17</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -5941,17 +5997,17 @@
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>2027/7/18</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C40" s="16" t="n">
+      <c r="C40" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -5961,17 +6017,17 @@
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>2027/7/19</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>星期一</t>
         </is>
       </c>
-      <c r="C41" s="16" t="n">
+      <c r="C41" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -5981,17 +6037,17 @@
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>2027/7/20</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>星期二</t>
         </is>
       </c>
-      <c r="C42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -6001,17 +6057,17 @@
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>2027/7/21</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>星期三</t>
         </is>
       </c>
-      <c r="C43" s="16" t="n">
+      <c r="C43" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -6021,17 +6077,17 @@
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>2027/7/22</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>星期四</t>
         </is>
       </c>
-      <c r="C44" s="16" t="n">
+      <c r="C44" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -6041,17 +6097,17 @@
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>2027/7/23</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>星期五</t>
         </is>
       </c>
-      <c r="C45" s="16" t="n">
+      <c r="C45" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -6061,17 +6117,17 @@
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>2027/7/24</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C46" s="16" t="n">
+      <c r="C46" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -6081,17 +6137,17 @@
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>2027/7/25</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -6101,17 +6157,17 @@
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>2027/7/26</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>星期一</t>
         </is>
       </c>
-      <c r="C48" s="16" t="n">
+      <c r="C48" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -6121,17 +6177,17 @@
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>2027/7/27</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>星期二</t>
         </is>
       </c>
-      <c r="C49" s="16" t="n">
+      <c r="C49" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -6141,17 +6197,17 @@
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>2027/7/28</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>星期三</t>
         </is>
       </c>
-      <c r="C50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -6161,17 +6217,17 @@
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>2027/7/29</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>星期四</t>
         </is>
       </c>
-      <c r="C51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -6181,17 +6237,17 @@
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>2027/7/30</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>星期五</t>
         </is>
       </c>
-      <c r="C52" s="16" t="n">
+      <c r="C52" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -6201,17 +6257,17 @@
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>2027/7/31</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -6221,17 +6277,17 @@
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>2027/8/1</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C54" s="16" t="n">
+      <c r="C54" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -6241,17 +6297,17 @@
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="16" t="inlineStr">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>2027/8/2</t>
         </is>
       </c>
-      <c r="B55" s="16" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>星期一</t>
         </is>
       </c>
-      <c r="C55" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -6261,17 +6317,17 @@
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="16" t="inlineStr">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>2027/8/3</t>
         </is>
       </c>
-      <c r="B56" s="16" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>星期二</t>
         </is>
       </c>
-      <c r="C56" s="16" t="n">
+      <c r="C56" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -6281,17 +6337,17 @@
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>2027/8/4</t>
         </is>
       </c>
-      <c r="B57" s="16" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
         <is>
           <t>星期三</t>
         </is>
       </c>
-      <c r="C57" s="16" t="n">
+      <c r="C57" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -6301,17 +6357,17 @@
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>2027/8/5</t>
         </is>
       </c>
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="17" t="inlineStr">
         <is>
           <t>星期四</t>
         </is>
       </c>
-      <c r="C58" s="16" t="n">
+      <c r="C58" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -6321,17 +6377,17 @@
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="16" t="inlineStr">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>2027/8/6</t>
         </is>
       </c>
-      <c r="B59" s="16" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>星期五</t>
         </is>
       </c>
-      <c r="C59" s="16" t="n">
+      <c r="C59" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -6341,17 +6397,17 @@
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="16" t="inlineStr">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t>2027/8/7</t>
         </is>
       </c>
-      <c r="B60" s="16" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C60" s="16" t="n">
+      <c r="C60" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -6361,17 +6417,17 @@
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t>2027/8/8</t>
         </is>
       </c>
-      <c r="B61" s="16" t="inlineStr">
+      <c r="B61" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C61" s="16" t="n">
+      <c r="C61" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -6381,17 +6437,17 @@
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="16" t="inlineStr">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t>2027/8/9</t>
         </is>
       </c>
-      <c r="B62" s="16" t="inlineStr">
+      <c r="B62" s="17" t="inlineStr">
         <is>
           <t>星期一</t>
         </is>
       </c>
-      <c r="C62" s="16" t="n">
+      <c r="C62" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -6401,17 +6457,17 @@
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
+      <c r="A63" s="17" t="inlineStr">
         <is>
           <t>2027/8/10</t>
         </is>
       </c>
-      <c r="B63" s="16" t="inlineStr">
+      <c r="B63" s="17" t="inlineStr">
         <is>
           <t>星期二</t>
         </is>
       </c>
-      <c r="C63" s="16" t="n">
+      <c r="C63" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -6421,17 +6477,17 @@
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="16" t="inlineStr">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>2027/8/11</t>
         </is>
       </c>
-      <c r="B64" s="16" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>星期三</t>
         </is>
       </c>
-      <c r="C64" s="16" t="n">
+      <c r="C64" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -6441,17 +6497,17 @@
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="16" t="inlineStr">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t>2027/8/12</t>
         </is>
       </c>
-      <c r="B65" s="16" t="inlineStr">
+      <c r="B65" s="17" t="inlineStr">
         <is>
           <t>星期四</t>
         </is>
       </c>
-      <c r="C65" s="16" t="n">
+      <c r="C65" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -6461,17 +6517,17 @@
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="16" t="inlineStr">
+      <c r="A66" s="17" t="inlineStr">
         <is>
           <t>2027/8/13</t>
         </is>
       </c>
-      <c r="B66" s="16" t="inlineStr">
+      <c r="B66" s="17" t="inlineStr">
         <is>
           <t>星期五</t>
         </is>
       </c>
-      <c r="C66" s="16" t="n">
+      <c r="C66" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -6481,17 +6537,17 @@
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="16" t="inlineStr">
+      <c r="A67" s="17" t="inlineStr">
         <is>
           <t>2027/9/18</t>
         </is>
       </c>
-      <c r="B67" s="16" t="inlineStr">
+      <c r="B67" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C67" s="16" t="n">
+      <c r="C67" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -6501,17 +6557,17 @@
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="16" t="inlineStr">
+      <c r="A68" s="17" t="inlineStr">
         <is>
           <t>2027/9/19</t>
         </is>
       </c>
-      <c r="B68" s="16" t="inlineStr">
+      <c r="B68" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C68" s="16" t="n">
+      <c r="C68" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -6521,17 +6577,17 @@
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="16" t="inlineStr">
+      <c r="A69" s="17" t="inlineStr">
         <is>
           <t>2027/9/26</t>
         </is>
       </c>
-      <c r="B69" s="16" t="inlineStr">
+      <c r="B69" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C69" s="16" t="n">
+      <c r="C69" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -6541,17 +6597,17 @@
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="16" t="inlineStr">
+      <c r="A70" s="17" t="inlineStr">
         <is>
           <t>2027/9/28</t>
         </is>
       </c>
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="17" t="inlineStr">
         <is>
           <t>星期二</t>
         </is>
       </c>
-      <c r="C70" s="16" t="n">
+      <c r="C70" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -6561,17 +6617,17 @@
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="16" t="inlineStr">
+      <c r="A71" s="17" t="inlineStr">
         <is>
           <t>2027/10/2</t>
         </is>
       </c>
-      <c r="B71" s="16" t="inlineStr">
+      <c r="B71" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C71" s="16" t="n">
+      <c r="C71" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -6581,17 +6637,17 @@
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="16" t="inlineStr">
+      <c r="A72" s="17" t="inlineStr">
         <is>
           <t>2027/10/3</t>
         </is>
       </c>
-      <c r="B72" s="16" t="inlineStr">
+      <c r="B72" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C72" s="16" t="n">
+      <c r="C72" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -6601,17 +6657,17 @@
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="16" t="inlineStr">
+      <c r="A73" s="17" t="inlineStr">
         <is>
           <t>2027/10/9</t>
         </is>
       </c>
-      <c r="B73" s="16" t="inlineStr">
+      <c r="B73" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C73" s="16" t="n">
+      <c r="C73" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -6621,17 +6677,17 @@
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="16" t="inlineStr">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t>2027/10/10</t>
         </is>
       </c>
-      <c r="B74" s="16" t="inlineStr">
+      <c r="B74" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C74" s="16" t="n">
+      <c r="C74" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -6641,17 +6697,17 @@
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="16" t="inlineStr">
+      <c r="A75" s="17" t="inlineStr">
         <is>
           <t>2027/10/16</t>
         </is>
       </c>
-      <c r="B75" s="16" t="inlineStr">
+      <c r="B75" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C75" s="16" t="n">
+      <c r="C75" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -6661,17 +6717,17 @@
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="16" t="inlineStr">
+      <c r="A76" s="17" t="inlineStr">
         <is>
           <t>2027/10/17</t>
         </is>
       </c>
-      <c r="B76" s="16" t="inlineStr">
+      <c r="B76" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C76" s="16" t="n">
+      <c r="C76" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -6681,17 +6737,17 @@
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="16" t="inlineStr">
+      <c r="A77" s="17" t="inlineStr">
         <is>
           <t>2027/10/24</t>
         </is>
       </c>
-      <c r="B77" s="16" t="inlineStr">
+      <c r="B77" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C77" s="16" t="n">
+      <c r="C77" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -6701,17 +6757,17 @@
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="16" t="inlineStr">
+      <c r="A78" s="17" t="inlineStr">
         <is>
           <t>2027/10/31</t>
         </is>
       </c>
-      <c r="B78" s="16" t="inlineStr">
+      <c r="B78" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C78" s="16" t="n">
+      <c r="C78" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -6721,17 +6777,17 @@
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="16" t="inlineStr">
+      <c r="A79" s="17" t="inlineStr">
         <is>
           <t>2027/11/6</t>
         </is>
       </c>
-      <c r="B79" s="16" t="inlineStr">
+      <c r="B79" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C79" s="16" t="n">
+      <c r="C79" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -6741,17 +6797,17 @@
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="16" t="inlineStr">
+      <c r="A80" s="17" t="inlineStr">
         <is>
           <t>2027/11/7</t>
         </is>
       </c>
-      <c r="B80" s="16" t="inlineStr">
+      <c r="B80" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C80" s="16" t="n">
+      <c r="C80" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -6761,17 +6817,17 @@
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="16" t="inlineStr">
+      <c r="A81" s="17" t="inlineStr">
         <is>
           <t>2027/11/13</t>
         </is>
       </c>
-      <c r="B81" s="16" t="inlineStr">
+      <c r="B81" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C81" s="16" t="n">
+      <c r="C81" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -6781,17 +6837,17 @@
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="16" t="inlineStr">
+      <c r="A82" s="17" t="inlineStr">
         <is>
           <t>2027/11/14</t>
         </is>
       </c>
-      <c r="B82" s="16" t="inlineStr">
+      <c r="B82" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C82" s="16" t="n">
+      <c r="C82" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -6801,17 +6857,17 @@
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="16" t="inlineStr">
+      <c r="A83" s="17" t="inlineStr">
         <is>
           <t>2027/11/20</t>
         </is>
       </c>
-      <c r="B83" s="16" t="inlineStr">
+      <c r="B83" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C83" s="16" t="n">
+      <c r="C83" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -6821,17 +6877,17 @@
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="16" t="inlineStr">
+      <c r="A84" s="17" t="inlineStr">
         <is>
           <t>2027/11/21</t>
         </is>
       </c>
-      <c r="B84" s="16" t="inlineStr">
+      <c r="B84" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C84" s="16" t="n">
+      <c r="C84" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -6841,17 +6897,17 @@
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="16" t="inlineStr">
+      <c r="A85" s="17" t="inlineStr">
         <is>
           <t>2027/11/28</t>
         </is>
       </c>
-      <c r="B85" s="16" t="inlineStr">
+      <c r="B85" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C85" s="16" t="n">
+      <c r="C85" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -6861,17 +6917,17 @@
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="16" t="inlineStr">
+      <c r="A86" s="17" t="inlineStr">
         <is>
           <t>2027/12/4</t>
         </is>
       </c>
-      <c r="B86" s="16" t="inlineStr">
+      <c r="B86" s="17" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C86" s="16" t="n">
+      <c r="C86" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -6881,22 +6937,62 @@
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="16" t="inlineStr">
+      <c r="A87" s="17" t="inlineStr">
         <is>
           <t>2027/12/5</t>
         </is>
       </c>
-      <c r="B87" s="16" t="inlineStr">
+      <c r="B87" s="17" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C87" s="16" t="n">
+      <c r="C87" s="17" t="n">
         <v>3</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
           <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>2027/12/11</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、好好讀楞嚴（善覺）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t>2027/12/12</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C89" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
         </is>
       </c>
     </row>
@@ -6916,7 +7012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6924,134 +7020,168 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>2027 行事曆更新說明</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>更新項目</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>華嚴海會</t>
+          <t>華嚴海會（含前置作業）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>期間</t>
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>前置作業</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>2027/12/11（星期六）– 2027/12/22（星期三）</t>
+          <t>2027/12/13（星期一）– 2027/12/14（星期二），共 2 天</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>天數</t>
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>法會期間</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>共 12 天</t>
+          <t>2027/12/15（星期三）– 2027/12/26（星期日），共 12 天</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>封鎖區間</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>2027/12/13 – 2027/12/26，合計 14 天</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>原排程</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>歲末大型華嚴法會：2027/12/25 – 2028/1/2</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>異動內容 1</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>刪除 2027/12/25–12/31 之「歲末大型華嚴法會」，改為 2027/12/11–12/22「華嚴海會」，共 12 天。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>刪除原「歲末大型華嚴法會」2027/12/25–2028/1/2。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>異動內容 2</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>華嚴海會為重大活動，2027/12/11–12/22 期間原排定之所有活動全數取消，該 12 天僅保留華嚴海會。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="92" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>新增「華嚴海會前置作業」12/13–12/14（2 天）與「華嚴海會」12/15–12/26（12 天）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>異動內容 3</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>華嚴海會為重大活動，12/13–12/26 期間原排定之所有活動全數取消，該 14 天僅保留前置作業與華嚴海會。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>取消活動明細</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>秋季班：12/11、12/12、12/13、12/14、12/15、12/16、12/17、12/18、12/19、12/20、12/21、12/22（共 12 場／日）
-好好讀楞嚴（善覺）：12/11（共 1 場／日）
-兒童哲學班（秋季）：12/12、12/19（共 2 場／日）
-企業專班：台中：12/12（共 1 場／日）
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>秋季班：12/13、12/14、12/15、12/16、12/17、12/18、12/19、12/20、12/21、12/22、12/23、12/24（共 12 場／日）
 一日禪（新加坡）：12/18（共 1 場／日）
+兒童哲學班（秋季）：12/19、12/26（共 2 場／日）
 楞嚴經（新加坡）：12/19（共 1 場／日）</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>連帶調整</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>兒童哲學班（秋季）14 堂→12 堂；企業專班：台中 8 堂→7 堂；好好讀楞嚴：板橋 7 堂→6 堂；一日禪（新加坡）8 堂→7 堂；楞嚴經（新加坡）8 堂→7 堂；秋季班原 9/13–12/24 共 15 週，12/11–12/22 停課，實際上課 9/13–12/10、12/23–12/24。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>秋季班原 9/13–12/24 共 15 週，12/13 起停課，實際上課 9/13–12/10 共 13 週；兒童哲學班（秋季）14 堂→12 堂（取消 12/19、12/26）；一日禪（新加坡）8 堂→7 堂（取消 12/18）；楞嚴經（新加坡）8 堂→7 堂（取消 12/19）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>未受影響</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴（善覺）12/11、企業專班：台中 12/12、兒童哲學班（秋季）12/12 均在封鎖區間之前，維持原排程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>其他說明</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>除上述異動外，其餘月份與活動內容均與原 2027 行事曆相同。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>製作日期</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>2026/10/05</t>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>2026/10/06</t>
         </is>
       </c>
     </row>

--- a/行事曆/2027行事曆_華嚴海會更新版.xlsx
+++ b/行事曆/2027行事曆_華嚴海會更新版.xlsx
@@ -9,16 +9,19 @@
   <sheets>
     <sheet name="2027行事曆" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="活動總表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="活動重疊檢查" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="更新說明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="見輝法師授課" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="活動重疊檢查" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="更新說明" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'2027行事曆'!$A$1:$G$102</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'活動總表'!$20:$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'活動總表'!$A$1:$G$54</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'活動重疊檢查'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'活動重疊檢查'!$A$1:$D$89</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'更新說明'!$A$1:$B$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'活動總表'!$21:$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'活動總表'!$A$1:$G$56</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'見輝法師授課'!$14:$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'見輝法師授課'!$A$1:$E$68</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'活動重疊檢查'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'活動重疊檢查'!$A$1:$D$90</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'更新說明'!$A$1:$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -94,7 +97,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +132,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FDF2D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -202,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -247,6 +255,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1279,13 +1290,14 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="73.5" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t>21（農2/14）
 新加坡禪七
 兒童哲學班（春季）
-楞嚴經（新加坡）</t>
+楞嚴經（新加坡）
+八關齋戒暨共修法會</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -2033,11 +2045,12 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="34" customHeight="1">
+    <row r="51" ht="46.5" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>20（農5/16）
-兒童哲學班（春季）</t>
+兒童哲學班（春季）
+八關齋戒暨共修法會</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2265,13 +2278,14 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
+    <row r="59" ht="73.5" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
           <t>18（農6/15）
 暑期班
 兒童夏令營 第2梯
-楞嚴經（新加坡）</t>
+楞嚴經（新加坡）
+八關齋戒暨共修法會</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -2776,12 +2790,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="46.5" customHeight="1">
+    <row r="75" ht="60" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
           <t>19（農8/19）
 秋季班
-楞嚴經（新加坡）</t>
+楞嚴經（新加坡）
+八關齋戒暨共修法會</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -3016,13 +3031,14 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
+    <row r="83" ht="73.5" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
           <t>17（農9/18）
 秋季班
 兒童哲學班（秋季）
-楞嚴經（新加坡）</t>
+楞嚴經（新加坡）
+八關齋戒暨共修法會</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -3301,13 +3317,14 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
+    <row r="92" ht="73.5" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
           <t>21（農10/24）
 秋季班
 兒童哲學班（秋季）
-楞嚴經（新加坡）</t>
+楞嚴經（新加坡）
+八關齋戒暨共修法會</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -3651,7 +3668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3971,124 +3988,112 @@
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="13" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>八關齋戒暨共修法會</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>共 6 場</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>2027/3/21、2027/6/20、2027/7/18、2027/9/19、2027/10/17、2027/11/21（每月第三個星期日；1、2、4、5、8、12 月逢法會停辦）</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="13" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>二、活動明細</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>日期／期間</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>類別</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>地點</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="46" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>2027/1/1、2027/1/2、2027/1/3、2027/1/9、2027/1/10、2027/1/16、2027/1/17、2027/1/23、2027/1/24、2027/1/30、2027/1/31</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>星期五～星期日</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>華嚴法會</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>法會／大型活動</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>10:00–17:00</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>各分院</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>1/1，及其後每週六、日；共 11 天</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>2027/1/11–2027/1/15</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>星期一～星期五</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>僧眾禪五第一梯次</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>僧眾修行</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>待確認</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>待確認</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2027/1/18–2027/1/22</t>
+          <t>2027/1/11–2027/1/15</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -4098,7 +4103,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>僧眾禪五第二梯次</t>
+          <t>僧眾禪五第一梯次</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -4121,22 +4126,22 @@
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2027/2/6</t>
+          <t>2027/1/18–2027/1/22</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期一～星期五</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>新春上燈法會</t>
+          <t>僧眾禪五第二梯次</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>法會／大型活動</t>
+          <t>僧眾修行</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -4146,34 +4151,30 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>各分院</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>農曆正月初一；依慣例辦理</t>
-        </is>
-      </c>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2027/2/7–2027/2/14</t>
+          <t>2027/2/6</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>星期日～星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>冬安居禪七</t>
+          <t>新春上燈法會</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>禪七／禪修</t>
+          <t>法會／大型活動</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -4183,34 +4184,34 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>待確認</t>
+          <t>各分院</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>大眾初二至初九</t>
+          <t>農曆正月初一；依慣例辦理</t>
         </is>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2027/3/2–2027/6/18</t>
+          <t>2027/2/7–2027/2/14</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>星期一～星期五（晚上）</t>
+          <t>星期日～星期日</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>春季班</t>
+          <t>冬安居禪七</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>一般課程</t>
+          <t>禪七／禪修</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -4220,34 +4221,34 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>各分院</t>
+          <t>待確認</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>共 17 週</t>
+          <t>大眾初二至初九</t>
         </is>
       </c>
     </row>
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2027/3/13–2027/3/21</t>
+          <t>2027/3/2–2027/6/18</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>星期六～星期日</t>
+          <t>星期一～星期五（晚上）</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>新加坡禪七</t>
+          <t>春季班</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>禪七／禪修</t>
+          <t>一般課程</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -4257,30 +4258,34 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
+          <t>各分院</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>共 17 週</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2027/4/3</t>
+          <t>2027/3/13–2027/3/21</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期六～星期日</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（台中）</t>
+          <t>新加坡禪七</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>分院活動</t>
+          <t>禪七／禪修</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -4290,7 +4295,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr"/>
@@ -4298,17 +4303,17 @@
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2027/4/4</t>
+          <t>2027/4/3</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（台北）</t>
+          <t>清明法會放蒙山（台中）</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -4323,7 +4328,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr"/>
@@ -4331,17 +4336,17 @@
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2027/4/10</t>
+          <t>2027/4/4</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（高雄）</t>
+          <t>清明法會放蒙山（台北）</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -4356,7 +4361,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善首講堂</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr"/>
@@ -4364,17 +4369,17 @@
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2027/4/11</t>
+          <t>2027/4/10</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（板橋）</t>
+          <t>清明法會放蒙山（高雄）</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -4389,7 +4394,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr"/>
@@ -4397,22 +4402,22 @@
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2027/5/8–2027/5/16</t>
+          <t>2027/4/11</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>星期六～星期日</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>浴佛節</t>
+          <t>清明法會放蒙山（板橋）</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>法會／大型活動</t>
+          <t>分院活動</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -4422,34 +4427,30 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>各分院</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>啟建</t>
-        </is>
-      </c>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr"/>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2027/6/23–2027/6/30</t>
+          <t>2027/5/8–2027/5/16</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>依各列日期</t>
+          <t>星期六～星期日</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>夏安居禪七第一梯次</t>
+          <t>浴佛節</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>禪七／禪修</t>
+          <t>法會／大型活動</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -4459,15 +4460,19 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>待確認</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr"/>
+          <t>各分院</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>啟建</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2027/7/2–2027/7/9</t>
+          <t>2027/6/23–2027/6/30</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -4477,7 +4482,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>夏安居禪七第二梯次</t>
+          <t>夏安居禪七第一梯次</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -4500,22 +4505,22 @@
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2027/7/12–2027/8/13</t>
+          <t>2027/7/2–2027/7/9</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>星期一～星期五（晚上）</t>
+          <t>依各列日期</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>暑期班</t>
+          <t>夏安居禪七第二梯次</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>一般課程</t>
+          <t>禪七／禪修</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -4525,7 +4530,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>各分院</t>
+          <t>待確認</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr"/>
@@ -4533,22 +4538,22 @@
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2027/8/8</t>
+          <t>2027/7/12–2027/8/13</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期一～星期五（晚上）</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>彰化供佛齋僧大會</t>
+          <t>暑期班</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>供佛齋僧</t>
+          <t>一般課程</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -4558,7 +4563,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>彰化</t>
+          <t>各分院</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr"/>
@@ -4566,22 +4571,22 @@
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2027/8/21–2027/8/28</t>
+          <t>2027/8/8</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>星期六～星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>盂蘭盆暨梁皇法會</t>
+          <t>彰化供佛齋僧大會</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>法會／大型活動</t>
+          <t>供佛齋僧</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -4591,7 +4596,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>各分院</t>
+          <t>彰化</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr"/>
@@ -4599,22 +4604,22 @@
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2027/8/29</t>
+          <t>2027/8/21–2027/8/28</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六～星期六</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>林口供佛齋僧大會</t>
+          <t>盂蘭盆暨梁皇法會</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>供佛齋僧</t>
+          <t>法會／大型活動</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -4624,7 +4629,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>林口</t>
+          <t>各分院</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
@@ -4632,240 +4637,236 @@
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
+          <t>2027/8/29</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>林口供佛齋僧大會</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>供佛齋僧</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>林口</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
           <t>2027/9/13–2027/12/10
 （原排至 12/24）</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>星期一～星期五（晚上）</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>秋季班</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>一般課程</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>待確認</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>各分院</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>原共 15 週；12/13 起因華嚴海會前置作業及法會停課，實際上課 9/13–12/10，共 13 週</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>2027/9/28</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>星期二</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>教師禪修營</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>禪七／禪修</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>待確認</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>待確認</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>新增活動</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>2027/12/13–2027/12/14</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>星期一～星期二</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>華嚴海會前置作業</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>法會／大型活動</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>待確認</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>各分院</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>共 2 天；華嚴海會前置準備，不排其他活動</t>
         </is>
       </c>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
+          <t>2027/12/13–2027/12/14</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>星期一～星期二</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>華嚴海會前置作業</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>法會／大型活動</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>各分院</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>共 2 天；華嚴海會前置準備，不排其他活動</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
           <t>2027/12/15–2027/12/26</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>星期三～星期日</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>華嚴海會</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>法會／大型活動</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>待確認</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>各分院</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>共 12 天（本次更新）；原「歲末大型華嚴法會」2027/12/25–2028/1/2 調整為本案；本期間為重大活動，原有之其他活動均已取消</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>2027/3/7 起每週日</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>每週日</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>兒童哲學班（春季）</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>兒童教育</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
+    <row r="44" ht="46" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>2027/3/21、2027/6/20、2027/7/18、2027/9/19、2027/10/17、2027/11/21</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>每月第三個星期日</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>八關齋戒暨共修法會</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>法會／大型活動</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>待確認</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F44" s="17" t="inlineStr">
         <is>
           <t>各分院</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>共 16 堂；日期詳見上方課程場次表</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>2027/9/26 起每週日</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>每週日</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>兒童哲學班（秋季）</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>兒童教育</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>待確認</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>各分院</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>共 12 堂（原 14 堂；12/19、12/26 因華嚴海會取消）；日期詳見上方課程場次表</t>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>共 6 場；配合全年度開課行事曆，遇華嚴海會、清明法會等法會之月份（1、2、4、5、8、12 月）停辦</t>
         </is>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2027/7/11–2027/7/17</t>
+          <t>2027/3/7 起每週日</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>星期日～星期六</t>
+          <t>每週日</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第1梯</t>
+          <t>兒童哲學班（春季）</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -4885,24 +4886,24 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>第 1 梯次</t>
+          <t>共 16 堂；日期詳見上方課程場次表</t>
         </is>
       </c>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2027/7/18–2027/7/24</t>
+          <t>2027/9/26 起每週日</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>星期日～星期六</t>
+          <t>每週日</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第2梯</t>
+          <t>兒童哲學班（秋季）</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -4922,14 +4923,14 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>第 2 梯次</t>
+          <t>共 12 堂（原 14 堂；12/19、12/26 因華嚴海會取消）；日期詳見上方課程場次表</t>
         </is>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2027/7/25–2027/7/31</t>
+          <t>2027/7/11–2027/7/17</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -4939,7 +4940,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第3梯</t>
+          <t>兒童夏令營 第1梯</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -4959,14 +4960,14 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>第 3 梯次</t>
+          <t>第 1 梯次</t>
         </is>
       </c>
     </row>
     <row r="48" ht="34" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>2027/8/1–2027/8/7</t>
+          <t>2027/7/18–2027/7/24</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -4976,7 +4977,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第4梯</t>
+          <t>兒童夏令營 第2梯</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -4996,14 +4997,14 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>第 4 梯次</t>
+          <t>第 2 梯次</t>
         </is>
       </c>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2027/8/8–2027/8/14</t>
+          <t>2027/7/25–2027/7/31</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -5013,7 +5014,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第5梯</t>
+          <t>兒童夏令營 第3梯</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -5033,125 +5034,125 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>第 5 梯次</t>
+          <t>第 3 梯次</t>
         </is>
       </c>
     </row>
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
+          <t>2027/8/1–2027/8/7</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>星期日～星期六</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>兒童夏令營 第4梯</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>兒童教育</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>各分院</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>第 4 梯次</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2027/8/8–2027/8/14</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>星期日～星期六</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>兒童夏令營 第5梯</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>兒童教育</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>各分院</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>第 5 梯次</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>2027/8/15–2027/8/20</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>星期日～星期五</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>兒童夏令營 第6梯</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>兒童教育</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>待確認</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>各分院</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>第 6 梯次</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="46" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>2027/1/2、2027/2/6、2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/7/3、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>依各列日期</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台北</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>企業專班</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>待確認</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>善首講堂</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>每月第一個星期六</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="46" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>2027/1/3、2027/2/7、2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/7/4、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>依各列日期</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：高雄</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>企業專班</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>待確認</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>圓道禪寺（高雄）</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>每月第一個星期日</t>
         </is>
       </c>
     </row>
     <row r="53" ht="46" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2027/1/10、2027/2/14、2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/8、2027/9/12、2027/10/10、2027/11/14、2027/12/12</t>
+          <t>2027/1/2、2027/2/6、2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/7/3、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -5161,7 +5162,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>企業專班：台北</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -5176,54 +5177,128 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>善首講堂</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>每月第二個星期日</t>
+          <t>每月第一個星期六</t>
         </is>
       </c>
     </row>
     <row r="54" ht="46" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
+          <t>2027/1/3、2027/2/7、2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/7/4、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>依各列日期</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>企業專班</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>每月第一個星期日</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="46" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>2027/1/10、2027/2/14、2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/8、2027/9/12、2027/10/10、2027/11/14、2027/12/12</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>依各列日期</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>企業專班</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>每月第二個星期日</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="46" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
           <t>2027/1/9、2027/2/13、2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/7/10、2027/8/14、2027/9/11、2027/10/9、2027/11/13、2027/12/11</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>依各列日期</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>好好讀楞嚴（善覺）</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>一般課程</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>待確認</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>善覺講堂</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>每月第二週週六</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
@@ -5231,6 +5306,7 @@
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C18:G18"/>
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="C5:G5"/>
@@ -5251,7 +5327,1321 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:E68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>見輝法師 2027 年授課一覽</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>合計 45 堂；日期落在華嚴海會封鎖區間（12/13–12/26）者已取消。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>一、課程總覽</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>課程</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>開課規則</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>地點</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>堂數</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>每月第一個星期六</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>8 堂</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/8/7、2027/10/2、2027/11/6、2027/12/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>每月第一個星期日</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>8 堂</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/10/3、2027/11/7、2027/12/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>每月第二個星期日</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>8 堂</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/8/8、2027/10/10、2027/11/14、2027/12/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>每月第二週週六</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>7 堂</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/10/9、2027/11/13、2027/12/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>一日禪（新加坡）</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>依各列日期</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>7 堂</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>2027/3/20、2027/4/17、2027/5/15、2027/7/17、2027/9/18、2027/10/16、2027/11/20　（取消：12/18）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>依各列日期</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>7 堂</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>2027/3/21、2027/4/18、2027/5/16、2027/7/18、2027/9/19、2027/10/17、2027/11/21　（取消：12/19）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>二、授課行程（依日期排序）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>星期</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>課程</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>地點</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>2027/3/6</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>2027/3/7</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>2027/3/13</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>2027/3/14</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>2027/3/20</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>一日禪（新加坡）</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>2027/3/21</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/3</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/4</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/10</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/11</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/17</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>一日禪（新加坡）</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/18</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="6" customHeight="1"/>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/1</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/2</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/8</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/9</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/15</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>一日禪（新加坡）</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/16</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="6" customHeight="1"/>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>2027/6/5</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>2027/6/6</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>2027/6/12</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>2027/6/13</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40" ht="6" customHeight="1"/>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/17</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>一日禪（新加坡）</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/18</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/1</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/7</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/8</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="6" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>2027/9/18</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>一日禪（新加坡）</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>2027/9/19</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50" ht="6" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/2</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/3</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/9</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/10</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/16</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>一日禪（新加坡）</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/17</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57" ht="6" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/6</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/7</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/13</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/14</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/20</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>一日禪（新加坡）</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/21</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64" ht="6" customHeight="1"/>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/4</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/5</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/11</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/12</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.3" right="0.3" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5297,17 +6687,17 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>2027/3/7</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -5317,17 +6707,17 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>2027/3/13</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -5337,17 +6727,17 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>2027/3/14</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -5357,17 +6747,17 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>2027/3/15</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>星期一</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -5377,17 +6767,17 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>2027/3/16</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>星期二</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -5397,17 +6787,17 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>2027/3/17</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>星期三</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -5417,17 +6807,17 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>2027/3/18</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>星期四</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -5437,17 +6827,17 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>2027/3/19</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>星期五</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -5457,17 +6847,17 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>2027/3/20</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -5477,1520 +6867,1540 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>2027/3/21</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>新加坡禪七、兒童哲學班（春季）、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/3</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>新加坡禪七、兒童哲學班（春季）、楞嚴經（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>2027/4/3</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>清明法會放蒙山（台中）、企業專班：善首、英文一日禪（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/4</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>清明法會放蒙山（台北）、兒童哲學班（春季）、企業專班：高雄</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/10</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>清明法會放蒙山（高雄）、好好讀楞嚴（善覺）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/11</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>清明法會放蒙山（台中）、企業專班：善首、英文一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>2027/4/4</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>清明法會放蒙山（板橋）、兒童哲學班（春季）、企業專班：台中</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/18</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C19" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>兒童哲學班（春季）、楞嚴經（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/1</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：善首、英文一日禪（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/2</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>清明法會放蒙山（台北）、兒童哲學班（春季）、企業專班：高雄</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>2027/4/10</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/8</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C22" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>清明法會放蒙山（高雄）、好好讀楞嚴（善覺）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>2027/4/11</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>浴佛節、好好讀楞嚴（善覺）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/9</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C23" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>清明法會放蒙山（板橋）、兒童哲學班（春季）、企業專班：台中</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>2027/4/18</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>浴佛節、兒童哲學班（春季）、企業專班：台中</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/10</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>星期一</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>春季班、浴佛節</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/11</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>星期二</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>春季班、浴佛節</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/12</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>星期三</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>春季班、浴佛節</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/13</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>星期四</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>春季班、浴佛節</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/14</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>星期五</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>春季班、浴佛節</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/15</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>浴佛節、一日禪（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/16</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C30" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>浴佛節、兒童哲學班（春季）、楞嚴經（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>2027/6/5</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>兒童哲學班（春季）、楞嚴經（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>2027/5/1</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：善首、英文一日禪（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>2027/6/6</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>2027/6/13</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>兒童哲學班（春季）、企業專班：台中</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>2027/6/20</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>兒童哲學班（春季）、八關齋戒暨共修法會</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/12</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>星期一</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第1梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/13</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>星期二</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第1梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/14</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>星期三</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第1梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/15</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>星期四</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第1梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/16</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>星期五</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第1梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/17</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C40" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第1梯、一日禪（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/18</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第2梯、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/19</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>星期一</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：善首、英文一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>2027/5/2</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第2梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/20</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>星期二</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第2梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/21</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>星期三</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第2梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/22</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>星期四</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第2梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/23</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>星期五</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第2梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/24</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第2梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/25</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C48" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第3梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/26</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>星期一</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第3梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/27</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>星期二</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第3梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/28</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>星期三</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第3梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/29</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>星期四</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第3梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/30</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>星期五</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第3梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/31</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第3梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/1</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>2027/5/8</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第4梯、企業專班：高雄</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/2</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>星期一</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第4梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/3</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>星期二</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第4梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/4</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>星期三</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第4梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/5</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>星期四</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第4梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/6</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>星期五</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第4梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/7</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C61" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第4梯、企業專班：善首</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/8</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、彰化供佛齋僧大會、兒童夏令營 第5梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/9</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>星期一</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>浴佛節、好好讀楞嚴（善覺）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>2027/5/9</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第5梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/10</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>星期二</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第5梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/11</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>星期三</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第5梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/12</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>星期四</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第5梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/13</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>星期五</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>暑期班、兒童夏令營 第5梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>2027/9/18</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、一日禪（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>2027/9/19</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C23" s="17" t="n">
+      <c r="C69" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>浴佛節、兒童哲學班（春季）、企業專班：台中</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>2027/5/10</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>星期一</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="n">
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>2027/9/26</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>春季班、浴佛節</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>2027/5/11</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>2027/9/28</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
         <is>
           <t>星期二</t>
         </is>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C71" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>春季班、浴佛節</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>2027/5/12</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>星期三</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="n">
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、教師禪修營</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/2</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/3</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/9</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>春季班、浴佛節</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>2027/5/13</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>星期四</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="n">
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、好好讀楞嚴（善覺）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/10</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/16</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>春季班、浴佛節</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>2027/5/14</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>星期五</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="n">
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、一日禪（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/17</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/24</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>春季班、浴佛節</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>2027/5/15</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/31</t>
+        </is>
+      </c>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/6</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C80" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/7</t>
+        </is>
+      </c>
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/13</t>
+        </is>
+      </c>
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>浴佛節、一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>2027/5/16</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、好好讀楞嚴（善覺）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/14</t>
+        </is>
+      </c>
+      <c r="B83" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C83" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>浴佛節、兒童哲學班（春季）、楞嚴經（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>2027/6/5</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/20</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C31" s="17" t="n">
+      <c r="C84" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：善首、英文一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t>2027/6/6</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、一日禪（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/21</t>
+        </is>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C32" s="17" t="n">
+      <c r="C85" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/28</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/4</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t>2027/6/13</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/5</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C33" s="17" t="n">
+      <c r="C88" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/11</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>兒童哲學班（春季）、企業專班：台中</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/12</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>星期一</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第1梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/13</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>星期二</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第1梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/14</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>星期三</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第1梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/15</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>星期四</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第1梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/16</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>星期五</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第1梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/17</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="n">
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、好好讀楞嚴（善覺）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/12</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第1梯、一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/18</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第2梯、楞嚴經（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/19</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>星期一</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第2梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/20</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>星期二</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第2梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/21</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>星期三</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第2梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/22</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>星期四</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第2梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/23</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>星期五</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第2梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/24</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第2梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/25</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第3梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/26</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>星期一</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第3梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/27</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>星期二</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第3梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/28</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>星期三</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第3梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/29</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>星期四</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第3梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/30</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>星期五</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第3梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t>2027/7/31</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第3梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/1</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第4梯、企業專班：高雄</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/2</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>星期一</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第4梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/3</t>
-        </is>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>星期二</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第4梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/4</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>星期三</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第4梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/5</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>星期四</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第4梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/6</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>星期五</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第4梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/7</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第4梯、企業專班：善首</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/8</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C61" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、彰化供佛齋僧大會、兒童夏令營 第5梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/9</t>
-        </is>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>星期一</t>
-        </is>
-      </c>
-      <c r="C62" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第5梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/10</t>
-        </is>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>星期二</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第5梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/11</t>
-        </is>
-      </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>星期三</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第5梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/12</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>星期四</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第5梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="17" t="inlineStr">
-        <is>
-          <t>2027/8/13</t>
-        </is>
-      </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>星期五</t>
-        </is>
-      </c>
-      <c r="C66" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>暑期班、兒童夏令營 第5梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="17" t="inlineStr">
-        <is>
-          <t>2027/9/18</t>
-        </is>
-      </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C67" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="17" t="inlineStr">
-        <is>
-          <t>2027/9/19</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C68" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、楞嚴經（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="17" t="inlineStr">
-        <is>
-          <t>2027/9/26</t>
-        </is>
-      </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C69" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、兒童哲學班（秋季）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="17" t="inlineStr">
-        <is>
-          <t>2027/9/28</t>
-        </is>
-      </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>星期二</t>
-        </is>
-      </c>
-      <c r="C70" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、教師禪修營</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="17" t="inlineStr">
-        <is>
-          <t>2027/10/2</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C71" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="17" t="inlineStr">
-        <is>
-          <t>2027/10/3</t>
-        </is>
-      </c>
-      <c r="B72" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C72" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="17" t="inlineStr">
-        <is>
-          <t>2027/10/9</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、好好讀楞嚴（善覺）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="17" t="inlineStr">
-        <is>
-          <t>2027/10/10</t>
-        </is>
-      </c>
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C74" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="17" t="inlineStr">
-        <is>
-          <t>2027/10/16</t>
-        </is>
-      </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C75" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="17" t="inlineStr">
-        <is>
-          <t>2027/10/17</t>
-        </is>
-      </c>
-      <c r="B76" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="17" t="inlineStr">
-        <is>
-          <t>2027/10/24</t>
-        </is>
-      </c>
-      <c r="B77" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C77" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、兒童哲學班（秋季）</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="17" t="inlineStr">
-        <is>
-          <t>2027/10/31</t>
-        </is>
-      </c>
-      <c r="B78" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C78" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、兒童哲學班（秋季）</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="17" t="inlineStr">
-        <is>
-          <t>2027/11/6</t>
-        </is>
-      </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="17" t="inlineStr">
-        <is>
-          <t>2027/11/7</t>
-        </is>
-      </c>
-      <c r="B80" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C80" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="17" t="inlineStr">
-        <is>
-          <t>2027/11/13</t>
-        </is>
-      </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C81" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、好好讀楞嚴（善覺）</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="17" t="inlineStr">
-        <is>
-          <t>2027/11/14</t>
-        </is>
-      </c>
-      <c r="B82" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C82" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="17" t="inlineStr">
-        <is>
-          <t>2027/11/20</t>
-        </is>
-      </c>
-      <c r="B83" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C83" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="17" t="inlineStr">
-        <is>
-          <t>2027/11/21</t>
-        </is>
-      </c>
-      <c r="B84" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C84" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="17" t="inlineStr">
-        <is>
-          <t>2027/11/28</t>
-        </is>
-      </c>
-      <c r="B85" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C85" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、兒童哲學班（秋季）</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/4</t>
-        </is>
-      </c>
-      <c r="B86" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C86" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/5</t>
-        </is>
-      </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C87" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/11</t>
-        </is>
-      </c>
-      <c r="B88" s="17" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C88" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、好好讀楞嚴（善覺）</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="17" t="inlineStr">
-        <is>
-          <t>2027/12/12</t>
-        </is>
-      </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C89" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
         </is>
@@ -7006,7 +8416,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7027,7 +8437,7 @@
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>更新項目</t>
         </is>
@@ -7039,7 +8449,7 @@
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>前置作業</t>
         </is>
@@ -7051,7 +8461,7 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>法會期間</t>
         </is>
@@ -7063,7 +8473,7 @@
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>封鎖區間</t>
         </is>
@@ -7075,7 +8485,7 @@
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>原排程</t>
         </is>
@@ -7087,7 +8497,7 @@
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>異動內容 1</t>
         </is>
@@ -7099,7 +8509,7 @@
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>異動內容 2</t>
         </is>
@@ -7111,7 +8521,7 @@
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>異動內容 3</t>
         </is>
@@ -7123,7 +8533,7 @@
       </c>
     </row>
     <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>取消活動明細</t>
         </is>
@@ -7138,7 +8548,7 @@
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>連帶調整</t>
         </is>
@@ -7150,7 +8560,7 @@
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>未受影響</t>
         </is>
@@ -7162,7 +8572,7 @@
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>其他說明</t>
         </is>
@@ -7174,14 +8584,14 @@
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>製作日期</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>2026/10/06</t>
+          <t>2026/10/07</t>
         </is>
       </c>
     </row>

--- a/行事曆/2027行事曆_華嚴海會更新版.xlsx
+++ b/行事曆/2027行事曆_華嚴海會更新版.xlsx
@@ -2479,13 +2479,14 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
+    <row r="65" ht="73.5" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
           <t>8（農7/7）
 暑期班
 彰化供佛齋僧大會
-兒童夏令營 第5梯</t>
+兒童夏令營 第5梯
+企業專班：台中</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -5152,7 +5153,7 @@
     <row r="53" ht="46" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2027/1/2、2027/2/6、2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/7/3、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4</t>
+          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/8/7、2027/10/2、2027/11/6、2027/12/4</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -5182,14 +5183,14 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>每月第一個星期六</t>
+          <t>每月第一個星期六；共 8 堂（3 月起）</t>
         </is>
       </c>
     </row>
     <row r="54" ht="46" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2027/1/3、2027/2/7、2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/7/4、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5</t>
+          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/10/3、2027/11/7、2027/12/5</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -5219,14 +5220,14 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>每月第一個星期日</t>
+          <t>每月第一個星期日；共 8 堂（3 月起）</t>
         </is>
       </c>
     </row>
     <row r="55" ht="46" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>2027/1/10、2027/2/14、2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/8、2027/9/12、2027/10/10、2027/11/14、2027/12/12</t>
+          <t>2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/8/8、2027/10/10、2027/11/14、2027/12/12</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -5256,14 +5257,14 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>每月第二個星期日</t>
+          <t>每月第二個星期日；共 8 堂（3 月起）</t>
         </is>
       </c>
     </row>
     <row r="56" ht="46" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>2027/1/9、2027/2/13、2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/7/10、2027/8/14、2027/9/11、2027/10/9、2027/11/13、2027/12/11</t>
+          <t>2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/10/9、2027/11/13、2027/12/11</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -5293,7 +5294,7 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>每月第二週週六</t>
+          <t>每月第二週週六；共 7 堂（3 月起）</t>
         </is>
       </c>
     </row>
@@ -7838,11 +7839,11 @@
         </is>
       </c>
       <c r="C62" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>暑期班、彰化供佛齋僧大會、兒童夏令營 第5梯</t>
+          <t>暑期班、彰化供佛齋僧大會、兒童夏令營 第5梯、企業專班：台中</t>
         </is>
       </c>
     </row>

--- a/行事曆/2027行事曆_華嚴海會更新版.xlsx
+++ b/行事曆/2027行事曆_華嚴海會更新版.xlsx
@@ -18,10 +18,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'活動總表'!$21:$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'活動總表'!$A$1:$G$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'見輝法師授課'!$14:$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'見輝法師授課'!$A$1:$E$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'見輝法師授課'!$A$1:$E$75</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'活動重疊檢查'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'活動重疊檢查'!$A$1:$D$90</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'更新說明'!$A$1:$B$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'活動重疊檢查'!$A$1:$D$94</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'更新說明'!$A$1:$B$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1232,9 +1232,7 @@
       <c r="G24" s="6" t="inlineStr">
         <is>
           <t>13（農2/6）
-新加坡禪七
-好好讀楞嚴（善覺）
-英文一日禪（新加坡）</t>
+新加坡禪七</t>
         </is>
       </c>
     </row>
@@ -1243,8 +1241,7 @@
         <is>
           <t>14（農2/7）
 新加坡禪七
-兒童哲學班（春季）
-企業專班：台中</t>
+兒童哲學班（春季）</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1290,14 +1287,14 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="73.5" customHeight="1">
+    <row r="26" ht="100.5" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t>21（農2/14）
 新加坡禪七
 兒童哲學班（春季）
-楞嚴經（新加坡）
-八關齋戒暨共修法會</t>
+八關齋戒暨共修法會
+企業專班：台中</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1336,7 +1333,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="34" customHeight="1">
+    <row r="27" ht="46.5" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t>28（農2/21）
@@ -1430,12 +1427,11 @@
         <is>
           <t>3（農2/27）
 清明法會放蒙山（台中）
-企業專班：善首
-英文一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
+企業專班：善首</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="87" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t>4（農2/28）
@@ -1482,7 +1478,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
+    <row r="33" ht="87" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t>11（農3/5）
@@ -1528,7 +1524,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="46.5" customHeight="1">
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>18（農3/12）
@@ -1572,7 +1568,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="34" customHeight="1">
+    <row r="35" ht="46.5" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t>25（農3/19）
@@ -1655,7 +1651,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="46.5" customHeight="1">
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="5" t="n"/>
@@ -1670,7 +1666,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
+    <row r="40" ht="87" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t>2（農3/26）
@@ -1712,16 +1708,16 @@
       <c r="G40" s="6" t="inlineStr">
         <is>
           <t>8（農4/3）
-浴佛節
-好好讀楞嚴（善覺）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="60" customHeight="1">
+浴佛節法會
+好好讀楞嚴（善覺） 14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="73.5" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>9（農4/4）
-浴佛節
+浴佛週
 兒童哲學班（春季）
 企業專班：台中</t>
         </is>
@@ -1730,50 +1726,50 @@
         <is>
           <t>10（農4/5）
 春季班
-浴佛節</t>
+浴佛週</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
           <t>11（農4/6）
 春季班
-浴佛節</t>
+浴佛週</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
           <t>12（農4/7）
 春季班
-浴佛節</t>
+浴佛週</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
           <t>13（農4/8）
 春季班
-浴佛節</t>
+浴佛週</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
           <t>14（農4/9）
 春季班
-浴佛節</t>
+浴佛週</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
           <t>15（農4/10）
-浴佛節
+浴佛週
 一日禪（新加坡）</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
+    <row r="42" ht="73.5" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
           <t>16（農4/11）
-浴佛節
+浴佛週
 兒童哲學班（春季）
 楞嚴經（新加坡）</t>
         </is>
@@ -1814,7 +1810,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1">
+    <row r="43" ht="46.5" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t>23（農4/18）
@@ -1857,7 +1853,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="34" customHeight="1">
+    <row r="44" ht="46.5" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
           <t>30（農4/25）
@@ -1920,7 +1916,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="46.5" customHeight="1">
+    <row r="48" ht="60" customHeight="1">
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6" t="inlineStr">
@@ -1955,7 +1951,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
+    <row r="49" ht="87" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
           <t>6（農5/2）
@@ -2001,7 +1997,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="46.5" customHeight="1">
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
           <t>13（農5/9）
@@ -2045,7 +2041,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="46.5" customHeight="1">
+    <row r="51" ht="73.5" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>20（農5/16）
@@ -2088,7 +2084,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="34" customHeight="1">
+    <row r="52" ht="46.5" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
           <t>27（農5/23）
@@ -2161,7 +2157,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="34" customHeight="1">
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="5" t="n"/>
@@ -2180,15 +2176,17 @@
       <c r="G56" s="6" t="inlineStr">
         <is>
           <t>3（農5/29）
-夏安居禪七第二梯次</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="34" customHeight="1">
+夏安居禪七第二梯次
+企業專班：善首</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
           <t>4（農6/1）
-夏安居禪七第二梯次</t>
+夏安居禪七第二梯次
+企業專班：高雄</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -2223,7 +2221,8 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>10（農6/7）</t>
+          <t>10（農6/7）
+好好讀楞嚴（善覺）</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2230,8 @@
       <c r="A58" s="6" t="inlineStr">
         <is>
           <t>11（農6/8）
-兒童夏令營 第1梯</t>
+兒童夏令營 第1梯
+企業專班：台中</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -2278,14 +2278,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="73.5" customHeight="1">
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
           <t>18（農6/15）
 暑期班
 兒童夏令營 第2梯
-楞嚴經（新加坡）
-八關齋戒暨共修法會</t>
+楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -2479,14 +2478,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="73.5" customHeight="1">
+    <row r="65" ht="60" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
           <t>8（農7/7）
 暑期班
 彰化供佛齋僧大會
-兒童夏令營 第5梯
-企業專班：台中</t>
+兒童夏令營 第5梯</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -2527,15 +2525,17 @@
       <c r="G65" s="6" t="inlineStr">
         <is>
           <t>14（農7/13）
-兒童夏令營 第5梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="34" customHeight="1">
+兒童夏令營 第5梯
+好好讀楞嚴（善覺）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="46.5" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
           <t>15（農7/14）
-兒童夏令營 第6梯</t>
+兒童夏令營 第6梯
+企業專班：台中</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -2706,14 +2706,16 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>4（農8/4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="34" customHeight="1">
+          <t>4（農8/4）
+企業專班：善首</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="46.5" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>5（農8/5）</t>
+          <t>5（農8/5）
+企業專班：高雄</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -2743,14 +2745,16 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>11（農8/11）</t>
+          <t>11（農8/11）
+好好讀楞嚴（善覺）</t>
         </is>
       </c>
     </row>
     <row r="74" ht="46.5" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>12（農8/12）</t>
+          <t>12（農8/12）
+企業專班：台中</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -2791,7 +2795,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
+    <row r="75" ht="73.5" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
           <t>19（農8/19）
@@ -2837,7 +2841,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="46.5" customHeight="1">
+    <row r="76" ht="60" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
           <t>26（農8/26）
@@ -2917,7 +2921,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
+    <row r="80" ht="73.5" customHeight="1">
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="5" t="n"/>
@@ -2938,7 +2942,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
+    <row r="81" ht="73.5" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
           <t>3（農9/4）
@@ -2985,7 +2989,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
+    <row r="82" ht="73.5" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
           <t>10（農9/11）
@@ -3032,7 +3036,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="73.5" customHeight="1">
+    <row r="83" ht="100.5" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
           <t>17（農9/18）
@@ -3079,7 +3083,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="46.5" customHeight="1">
+    <row r="84" ht="60" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
           <t>24（農9/25）
@@ -3124,7 +3128,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="46.5" customHeight="1">
+    <row r="85" ht="60" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
           <t>31（農10/3）
@@ -3183,7 +3187,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
+    <row r="89" ht="73.5" customHeight="1">
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="6" t="inlineStr">
         <is>
@@ -3224,7 +3228,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
+    <row r="90" ht="73.5" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
           <t>7（農10/10）
@@ -3271,7 +3275,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
+    <row r="91" ht="73.5" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
           <t>14（農10/17）
@@ -3318,7 +3322,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="73.5" customHeight="1">
+    <row r="92" ht="100.5" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
           <t>21（農10/24）
@@ -3365,7 +3369,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="46.5" customHeight="1">
+    <row r="93" ht="60" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
           <t>28（農11/1）
@@ -3434,7 +3438,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
+    <row r="97" ht="73.5" customHeight="1">
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="5" t="n"/>
@@ -3465,7 +3469,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
+    <row r="98" ht="73.5" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
           <t>5（農11/8）
@@ -3512,7 +3516,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
+    <row r="99" ht="73.5" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
           <t>12（農11/15）
@@ -3655,10 +3659,12 @@
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="3" manualBreakCount="3">
-    <brk id="28" min="0" max="16383" man="1"/>
+  <rowBreaks count="5" manualBreakCount="5">
+    <brk id="20" min="0" max="16383" man="1"/>
+    <brk id="36" min="0" max="16383" man="1"/>
     <brk id="53" min="0" max="16383" man="1"/>
-    <brk id="77" min="0" max="16383" man="1"/>
+    <brk id="69" min="0" max="16383" man="1"/>
+    <brk id="86" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -3829,12 +3835,12 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>共 8 堂</t>
+          <t>共 10 堂</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/8/7、2027/10/2、2027/11/6、2027/12/4</t>
+          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/7/3、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4　※ 7/3 加排（7 月場次補排）；9/4 加排（9 月場次補排）</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -3850,12 +3856,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>共 8 堂</t>
+          <t>共 10 堂</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/10/3、2027/11/7、2027/12/5</t>
+          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/7/4、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5　※ 7/4 加排（7 月場次補排）；9/5 加排（9 月場次補排）</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -3871,12 +3877,12 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>共 8 堂</t>
+          <t>共 10 堂</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/8/8、2027/10/10、2027/11/14、2027/12/12</t>
+          <t>2027/3/21、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/15、2027/9/12、2027/10/10、2027/11/14、2027/12/12　※ 3/14 改至 3/21（3/14 適逢新加坡禪七）；8/8 改至 8/15（8/8 彰化供佛齋僧大會）；7/11 加排（7 月場次補排）；9/12 加排（9 月場次補排）</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -3892,12 +3898,12 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>共 7 堂</t>
+          <t>共 9 堂</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/10/9、2027/11/13、2027/12/11</t>
+          <t>2027/4/10、2027/5/8、2027/6/12、2027/7/10、2027/8/14、2027/9/11、2027/10/9、2027/11/13、2027/12/11　※ 3/13 取消（3/13 三案重疊，以新加坡禪七為主）；8/14 加排（善覺講堂加排）；7/10 加排（7 月場次補排）；9/11 加排（9 月場次補排）；5/8 改為 14:00 上課</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -3913,12 +3919,12 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>共 8 堂</t>
+          <t>共 6 堂</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>2027/3/13、2027/4/3、2027/5/1、2027/6/5、2027/8/7、2027/10/2、2027/11/6、2027/12/4</t>
+          <t>2027/5/1、2027/6/5、2027/8/7、2027/10/2、2027/11/6、2027/12/4　※ 3/13 取消（3/13 三案重疊，以新加坡禪七為主）；4/3 取消（清明法會放蒙山（台中））</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -3960,7 +3966,7 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>2027/3/20、2027/4/17、2027/5/15、2027/7/17、2027/9/18、2027/10/16、2027/11/20（原 8 堂，12/18 因華嚴海會取消）</t>
+          <t>2027/3/20、2027/4/17、2027/5/15、2027/7/17、2027/9/18、2027/10/16、2027/11/20　※ 12/18 取消（華嚴海會）</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -3976,12 +3982,12 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>共 7 堂</t>
+          <t>共 6 堂</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>2027/3/21、2027/4/18、2027/5/16、2027/7/18、2027/9/19、2027/10/17、2027/11/21（原 8 堂，12/19 因華嚴海會取消）</t>
+          <t>2027/4/18、2027/5/16、2027/7/18、2027/9/19、2027/10/17、2027/11/21　※ 3/21 取消（合併至新加坡禪七）；12/19 取消（華嚴海會）</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -3997,12 +4003,12 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>共 6 場</t>
+          <t>共 5 場</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>2027/3/21、2027/6/20、2027/7/18、2027/9/19、2027/10/17、2027/11/21（每月第三個星期日；1、2、4、5、8、12 月逢法會停辦）</t>
+          <t>2027/3/21、2027/6/20、2027/9/19、2027/10/17、2027/11/21　※ 每月第三個星期日；停辦：1/17（華嚴法會）、2/21（新春上燈法會）、4/18（清明法會放蒙山（台中））、5/16（浴佛節法會）、7/18（兒童夏令營 第2梯）、8/15（盂蘭盆暨梁皇法會）、12/19（華嚴海會）</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -4817,10 +4823,10 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="46" customHeight="1">
+    <row r="44" ht="34" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>2027/3/21、2027/6/20、2027/7/18、2027/9/19、2027/10/17、2027/11/21</t>
+          <t>2027/3/21、2027/6/20、2027/9/19、2027/10/17、2027/11/21</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
@@ -4850,7 +4856,7 @@
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>共 6 場；配合全年度開課行事曆，遇華嚴海會、清明法會等法會之月份（1、2、4、5、8、12 月）停辦</t>
+          <t>共 5 場；配合全年度開課行事曆，遇華嚴海會、清明法會等法會之月份停辦。停辦：1/17（華嚴法會）、2/21（新春上燈法會）、4/18（清明法會放蒙山（台中））、5/16（浴佛節法會）、7/18（兒童夏令營 第2梯）、8/15（盂蘭盆暨梁皇法會）、12/19（華嚴海會）</t>
         </is>
       </c>
     </row>
@@ -5153,7 +5159,7 @@
     <row r="53" ht="46" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/8/7、2027/10/2、2027/11/6、2027/12/4</t>
+          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/7/3、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -5183,14 +5189,14 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>每月第一個星期六；共 8 堂（3 月起）</t>
+          <t>每月第一個星期六；共 10 堂；7/3 加排（7 月場次補排）；9/4 加排（9 月場次補排）</t>
         </is>
       </c>
     </row>
     <row r="54" ht="46" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/10/3、2027/11/7、2027/12/5</t>
+          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/7/4、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -5220,14 +5226,14 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>每月第一個星期日；共 8 堂（3 月起）</t>
+          <t>每月第一個星期日；共 10 堂；7/4 加排（7 月場次補排）；9/5 加排（9 月場次補排）</t>
         </is>
       </c>
     </row>
     <row r="55" ht="46" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/8/8、2027/10/10、2027/11/14、2027/12/12</t>
+          <t>2027/3/21、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/15、2027/9/12、2027/10/10、2027/11/14、2027/12/12</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -5257,14 +5263,14 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>每月第二個星期日；共 8 堂（3 月起）</t>
+          <t>每月第二個星期日；共 10 堂；3/14 改至 3/21（3/14 適逢新加坡禪七）；8/8 改至 8/15（8/8 彰化供佛齋僧大會）；7/11 加排（7 月場次補排）；9/12 加排（9 月場次補排）</t>
         </is>
       </c>
     </row>
     <row r="56" ht="46" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/10/9、2027/11/13、2027/12/11</t>
+          <t>2027/4/10、2027/5/8、2027/6/12、2027/7/10、2027/8/14、2027/9/11、2027/10/9、2027/11/13、2027/12/11</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -5294,7 +5300,7 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>每月第二週週六；共 7 堂（3 月起）</t>
+          <t>每月第二週週六；共 9 堂；3/13 取消（3/13 三案重疊，以新加坡禪七為主）；8/14 加排（善覺講堂加排）；7/10 加排（7 月場次補排）；9/11 加排（9 月場次補排）；5/8 改為 14:00 上課</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5348,7 +5354,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>合計 45 堂；日期落在華嚴海會封鎖區間（12/13–12/26）者已取消。</t>
+          <t>合計 52 堂；日期落在華嚴海會封鎖區間（12/13–12/26）者已取消。</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5410,12 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>8 堂</t>
+          <t>10 堂</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/8/7、2027/10/2、2027/11/6、2027/12/4</t>
+          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/7/3、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4</t>
         </is>
       </c>
     </row>
@@ -5431,12 +5437,12 @@
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>8 堂</t>
+          <t>10 堂</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/10/3、2027/11/7、2027/12/5</t>
+          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/7/4、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5</t>
         </is>
       </c>
     </row>
@@ -5458,12 +5464,12 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>8 堂</t>
+          <t>10 堂</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>2027/3/14、2027/4/11、2027/5/9、2027/6/13、2027/8/8、2027/10/10、2027/11/14、2027/12/12</t>
+          <t>2027/3/21、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/15、2027/9/12、2027/10/10、2027/11/14、2027/12/12</t>
         </is>
       </c>
     </row>
@@ -5485,12 +5491,12 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>7 堂</t>
+          <t>9 堂</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>2027/3/13、2027/4/10、2027/5/8、2027/6/12、2027/10/9、2027/11/13、2027/12/11</t>
+          <t>2027/4/10、2027/5/8、2027/6/12、2027/7/10、2027/8/14、2027/9/11、2027/10/9、2027/11/13、2027/12/11</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5545,12 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>7 堂</t>
+          <t>6 堂</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>2027/3/21、2027/4/18、2027/5/16、2027/7/18、2027/9/19、2027/10/17、2027/11/21　（取消：12/19）</t>
+          <t>2027/4/18、2027/5/16、2027/7/18、2027/9/19、2027/10/17、2027/11/21　（取消：12/19）</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5637,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>2027/3/13</t>
+          <t>2027/3/20</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
@@ -5641,12 +5647,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
@@ -5654,7 +5660,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>2027/3/14</t>
+          <t>2027/3/21</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
@@ -5674,57 +5680,57 @@
       </c>
       <c r="E18" s="6" t="inlineStr"/>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>2027/3/20</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>一日禪（新加坡）</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr"/>
-    </row>
+    <row r="19" ht="6" customHeight="1"/>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>2027/3/21</t>
+          <t>2027/4/3</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/4</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>楞嚴經（新加坡）</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21" ht="6" customHeight="1"/>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr"/>
+    </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>2027/4/3</t>
+          <t>2027/4/10</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
@@ -5734,12 +5740,12 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
@@ -5747,7 +5753,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>2027/4/4</t>
+          <t>2027/4/11</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
@@ -5757,12 +5763,12 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
@@ -5770,7 +5776,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>2027/4/10</t>
+          <t>2027/4/17</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
@@ -5780,12 +5786,12 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
@@ -5793,7 +5799,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>2027/4/11</t>
+          <t>2027/4/18</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
@@ -5803,67 +5809,67 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>2027/4/17</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>一日禪（新加坡）</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr"/>
-    </row>
+    <row r="26" ht="6" customHeight="1"/>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>2027/4/18</t>
+          <t>2027/5/1</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/2</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>楞嚴經（新加坡）</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28" ht="6" customHeight="1"/>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr"/>
+    </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>2027/5/1</t>
+          <t>2027/5/8</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
@@ -5873,12 +5879,12 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
@@ -5886,7 +5892,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>2027/5/2</t>
+          <t>2027/5/9</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
@@ -5896,12 +5902,12 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr"/>
@@ -5909,7 +5915,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>2027/5/8</t>
+          <t>2027/5/15</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
@@ -5919,12 +5925,12 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
@@ -5932,7 +5938,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>2027/5/9</t>
+          <t>2027/5/16</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
@@ -5942,67 +5948,67 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr"/>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>2027/5/15</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>一日禪（新加坡）</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr"/>
-    </row>
+    <row r="33" ht="6" customHeight="1"/>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>2027/5/16</t>
+          <t>2027/6/5</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>2027/6/6</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>楞嚴經（新加坡）</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35" ht="6" customHeight="1"/>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr"/>
+    </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>2027/6/5</t>
+          <t>2027/6/12</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
@@ -6012,12 +6018,12 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr"/>
@@ -6025,7 +6031,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>2027/6/6</t>
+          <t>2027/6/13</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
@@ -6035,67 +6041,67 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr"/>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>2027/6/12</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>好好讀楞嚴：板橋</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>善覺講堂</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr"/>
-    </row>
+    <row r="38" ht="6" customHeight="1"/>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>2027/6/13</t>
+          <t>2027/7/3</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/4</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台中</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40" ht="6" customHeight="1"/>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr"/>
+    </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>2027/7/17</t>
+          <t>2027/7/10</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
@@ -6105,12 +6111,12 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>一日禪（新加坡）</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>新加坡</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr"/>
@@ -6118,7 +6124,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>2027/7/18</t>
+          <t>2027/7/11</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
@@ -6128,21 +6134,43 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>楞嚴經（新加坡）</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/17</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>一日禪（新加坡）</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
           <t>新加坡</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43" ht="6" customHeight="1"/>
+      <c r="E43" s="6" t="inlineStr"/>
+    </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>2027/8/1</t>
+          <t>2027/7/18</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
@@ -6152,43 +6180,21 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr"/>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="18" t="inlineStr">
-        <is>
-          <t>2027/8/7</t>
-        </is>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台北</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>善首講堂</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr"/>
-    </row>
+    <row r="45" ht="6" customHeight="1"/>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>2027/8/8</t>
+          <t>2027/8/1</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
@@ -6198,21 +6204,43 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr"/>
     </row>
-    <row r="47" ht="6" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/7</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr"/>
+    </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>2027/9/18</t>
+          <t>2027/8/14</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
@@ -6222,12 +6250,12 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>一日禪（新加坡）</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>新加坡</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr"/>
@@ -6235,7 +6263,7 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>2027/9/19</t>
+          <t>2027/8/15</t>
         </is>
       </c>
       <c r="B49" s="18" t="inlineStr">
@@ -6245,12 +6273,12 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>楞嚴經（新加坡）</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>新加坡</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr"/>
@@ -6259,7 +6287,7 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>2027/10/2</t>
+          <t>2027/9/4</t>
         </is>
       </c>
       <c r="B51" s="18" t="inlineStr">
@@ -6282,7 +6310,7 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>2027/10/3</t>
+          <t>2027/9/5</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
@@ -6305,7 +6333,7 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>2027/10/9</t>
+          <t>2027/9/11</t>
         </is>
       </c>
       <c r="B53" s="18" t="inlineStr">
@@ -6328,7 +6356,7 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>2027/10/10</t>
+          <t>2027/9/12</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
@@ -6351,7 +6379,7 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>2027/10/16</t>
+          <t>2027/9/18</t>
         </is>
       </c>
       <c r="B55" s="18" t="inlineStr">
@@ -6374,7 +6402,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>2027/10/17</t>
+          <t>2027/9/19</t>
         </is>
       </c>
       <c r="B56" s="18" t="inlineStr">
@@ -6398,7 +6426,7 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>2027/11/6</t>
+          <t>2027/10/2</t>
         </is>
       </c>
       <c r="B58" s="18" t="inlineStr">
@@ -6421,7 +6449,7 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>2027/11/7</t>
+          <t>2027/10/3</t>
         </is>
       </c>
       <c r="B59" s="18" t="inlineStr">
@@ -6444,7 +6472,7 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>2027/11/13</t>
+          <t>2027/10/9</t>
         </is>
       </c>
       <c r="B60" s="18" t="inlineStr">
@@ -6467,7 +6495,7 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>2027/11/14</t>
+          <t>2027/10/10</t>
         </is>
       </c>
       <c r="B61" s="18" t="inlineStr">
@@ -6490,7 +6518,7 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="18" t="inlineStr">
         <is>
-          <t>2027/11/20</t>
+          <t>2027/10/16</t>
         </is>
       </c>
       <c r="B62" s="18" t="inlineStr">
@@ -6513,7 +6541,7 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>2027/11/21</t>
+          <t>2027/10/17</t>
         </is>
       </c>
       <c r="B63" s="18" t="inlineStr">
@@ -6537,7 +6565,7 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>2027/12/4</t>
+          <t>2027/11/6</t>
         </is>
       </c>
       <c r="B65" s="18" t="inlineStr">
@@ -6560,7 +6588,7 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>2027/12/5</t>
+          <t>2027/11/7</t>
         </is>
       </c>
       <c r="B66" s="18" t="inlineStr">
@@ -6583,7 +6611,7 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="18" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>2027/11/13</t>
         </is>
       </c>
       <c r="B67" s="18" t="inlineStr">
@@ -6606,25 +6634,164 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="18" t="inlineStr">
         <is>
+          <t>2027/11/14</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/20</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>一日禪（新加坡）</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/21</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71" ht="6" customHeight="1"/>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/4</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/5</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/11</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
           <t>2027/12/12</t>
         </is>
       </c>
-      <c r="B68" s="18" t="inlineStr">
+      <c r="B75" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>企業專班：台中</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr"/>
+      <c r="E75" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6642,7 +6809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6710,52 +6877,52 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>2027/3/13</t>
+          <t>2027/3/14</t>
         </is>
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C6" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>新加坡禪七、好好讀楞嚴（善覺）、英文一日禪（新加坡）</t>
+          <t>新加坡禪七、兒童哲學班（春季）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>2027/3/14</t>
+          <t>2027/3/15</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C7" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>新加坡禪七、兒童哲學班（春季）、企業專班：台中</t>
+          <t>春季班、新加坡禪七</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>2027/3/15</t>
+          <t>2027/3/16</t>
         </is>
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C8" s="18" t="n">
@@ -6770,12 +6937,12 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>2027/3/16</t>
+          <t>2027/3/17</t>
         </is>
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C9" s="18" t="n">
@@ -6790,12 +6957,12 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>2027/3/17</t>
+          <t>2027/3/18</t>
         </is>
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C10" s="18" t="n">
@@ -6810,12 +6977,12 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>2027/3/18</t>
+          <t>2027/3/19</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C11" s="18" t="n">
@@ -6830,12 +6997,12 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>2027/3/19</t>
+          <t>2027/3/20</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C12" s="18" t="n">
@@ -6843,59 +7010,59 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>春季班、新加坡禪七</t>
+          <t>新加坡禪七、一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>2027/3/20</t>
+          <t>2027/3/21</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>新加坡禪七、一日禪（新加坡）</t>
+          <t>新加坡禪七、兒童哲學班（春季）、八關齋戒暨共修法會、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>2027/3/21</t>
+          <t>2027/4/3</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>新加坡禪七、兒童哲學班（春季）、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+          <t>清明法會放蒙山（台中）、企業專班：善首</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>2027/4/3</t>
+          <t>2027/4/4</t>
         </is>
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C15" s="18" t="n">
@@ -6903,54 +7070,54 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（台中）、企業專班：善首、英文一日禪（新加坡）</t>
+          <t>清明法會放蒙山（台北）、兒童哲學班（春季）、企業專班：高雄</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>2027/4/4</t>
+          <t>2027/4/10</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（台北）、兒童哲學班（春季）、企業專班：高雄</t>
+          <t>清明法會放蒙山（高雄）、好好讀楞嚴（善覺）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>2027/4/10</t>
+          <t>2027/4/11</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（高雄）、好好讀楞嚴（善覺）</t>
+          <t>清明法會放蒙山（板橋）、兒童哲學班（春季）、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>2027/4/11</t>
+          <t>2027/4/18</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
@@ -6959,23 +7126,23 @@
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（板橋）、兒童哲學班（春季）、企業專班：台中</t>
+          <t>兒童哲學班（春季）、楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>2027/4/18</t>
+          <t>2027/5/1</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
@@ -6983,99 +7150,99 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>兒童哲學班（春季）、楞嚴經（新加坡）</t>
+          <t>企業專班：善首、英文一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>2027/5/1</t>
+          <t>2027/5/2</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>企業專班：善首、英文一日禪（新加坡）</t>
+          <t>兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>2027/5/2</t>
+          <t>2027/5/8</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
+          <t>浴佛節法會、好好讀楞嚴（善覺） 14:00</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>2027/5/8</t>
+          <t>2027/5/9</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>浴佛節、好好讀楞嚴（善覺）</t>
+          <t>浴佛週、兒童哲學班（春季）、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>2027/5/9</t>
+          <t>2027/5/10</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>浴佛節、兒童哲學班（春季）、企業專班：台中</t>
+          <t>春季班、浴佛週</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>2027/5/10</t>
+          <t>2027/5/11</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
@@ -7083,19 +7250,19 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>春季班、浴佛節</t>
+          <t>春季班、浴佛週</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>2027/5/11</t>
+          <t>2027/5/12</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
@@ -7103,19 +7270,19 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>春季班、浴佛節</t>
+          <t>春季班、浴佛週</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>2027/5/12</t>
+          <t>2027/5/13</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C26" s="18" t="n">
@@ -7123,19 +7290,19 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>春季班、浴佛節</t>
+          <t>春季班、浴佛週</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>2027/5/13</t>
+          <t>2027/5/14</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C27" s="18" t="n">
@@ -7143,19 +7310,19 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>春季班、浴佛節</t>
+          <t>春季班、浴佛週</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>2027/5/14</t>
+          <t>2027/5/15</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
@@ -7163,74 +7330,74 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>春季班、浴佛節</t>
+          <t>浴佛週、一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>2027/5/15</t>
+          <t>2027/5/16</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>浴佛節、一日禪（新加坡）</t>
+          <t>浴佛週、兒童哲學班（春季）、楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>2027/5/16</t>
+          <t>2027/6/5</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>浴佛節、兒童哲學班（春季）、楞嚴經（新加坡）</t>
+          <t>企業專班：善首、英文一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>2027/6/5</t>
+          <t>2027/6/6</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>企業專班：善首、英文一日禪（新加坡）</t>
+          <t>兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>2027/6/6</t>
+          <t>2027/6/13</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
@@ -7239,18 +7406,18 @@
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
+          <t>兒童哲學班（春季）、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>2027/6/13</t>
+          <t>2027/6/20</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
@@ -7263,19 +7430,19 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>兒童哲學班（春季）、企業專班：台中</t>
+          <t>兒童哲學班（春季）、八關齋戒暨共修法會</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>2027/6/20</t>
+          <t>2027/7/3</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C34" s="18" t="n">
@@ -7283,19 +7450,19 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>兒童哲學班（春季）、八關齋戒暨共修法會</t>
+          <t>夏安居禪七第二梯次、企業專班：善首</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>2027/7/12</t>
+          <t>2027/7/4</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C35" s="18" t="n">
@@ -7303,19 +7470,19 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第1梯</t>
+          <t>夏安居禪七第二梯次、企業專班：高雄</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>2027/7/13</t>
+          <t>2027/7/11</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C36" s="18" t="n">
@@ -7323,19 +7490,19 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第1梯</t>
+          <t>兒童夏令營 第1梯、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>2027/7/14</t>
+          <t>2027/7/12</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C37" s="18" t="n">
@@ -7350,12 +7517,12 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>2027/7/15</t>
+          <t>2027/7/13</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C38" s="18" t="n">
@@ -7370,12 +7537,12 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>2027/7/16</t>
+          <t>2027/7/14</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C39" s="18" t="n">
@@ -7390,92 +7557,92 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>2027/7/17</t>
+          <t>2027/7/15</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第1梯、一日禪（新加坡）</t>
+          <t>暑期班、兒童夏令營 第1梯</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>2027/7/18</t>
+          <t>2027/7/16</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C41" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第2梯、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+          <t>暑期班、兒童夏令營 第1梯</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>2027/7/19</t>
+          <t>2027/7/17</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第2梯</t>
+          <t>暑期班、兒童夏令營 第1梯、一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>2027/7/20</t>
+          <t>2027/7/18</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C43" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第2梯</t>
+          <t>暑期班、兒童夏令營 第2梯、楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>2027/7/21</t>
+          <t>2027/7/19</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
@@ -7490,12 +7657,12 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>2027/7/22</t>
+          <t>2027/7/20</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
@@ -7510,12 +7677,12 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>2027/7/23</t>
+          <t>2027/7/21</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
@@ -7530,12 +7697,12 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>2027/7/24</t>
+          <t>2027/7/22</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
@@ -7550,12 +7717,12 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>2027/7/25</t>
+          <t>2027/7/23</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
@@ -7563,19 +7730,19 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第3梯</t>
+          <t>暑期班、兒童夏令營 第2梯</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>2027/7/26</t>
+          <t>2027/7/24</t>
         </is>
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C49" s="18" t="n">
@@ -7583,19 +7750,19 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第3梯</t>
+          <t>暑期班、兒童夏令營 第2梯</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>2027/7/27</t>
+          <t>2027/7/25</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C50" s="18" t="n">
@@ -7610,12 +7777,12 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>2027/7/28</t>
+          <t>2027/7/26</t>
         </is>
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
@@ -7630,12 +7797,12 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>2027/7/29</t>
+          <t>2027/7/27</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
@@ -7650,12 +7817,12 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>2027/7/30</t>
+          <t>2027/7/28</t>
         </is>
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C53" s="18" t="n">
@@ -7670,12 +7837,12 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>2027/7/31</t>
+          <t>2027/7/29</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C54" s="18" t="n">
@@ -7690,32 +7857,32 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>2027/8/1</t>
+          <t>2027/7/30</t>
         </is>
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C55" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第4梯、企業專班：高雄</t>
+          <t>暑期班、兒童夏令營 第3梯</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>2027/8/2</t>
+          <t>2027/7/31</t>
         </is>
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C56" s="18" t="n">
@@ -7723,39 +7890,39 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第4梯</t>
+          <t>暑期班、兒童夏令營 第3梯</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>2027/8/3</t>
+          <t>2027/8/1</t>
         </is>
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C57" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第4梯</t>
+          <t>暑期班、兒童夏令營 第4梯、企業專班：高雄</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>2027/8/4</t>
+          <t>2027/8/2</t>
         </is>
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C58" s="18" t="n">
@@ -7770,12 +7937,12 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>2027/8/5</t>
+          <t>2027/8/3</t>
         </is>
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C59" s="18" t="n">
@@ -7790,12 +7957,12 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>2027/8/6</t>
+          <t>2027/8/4</t>
         </is>
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C60" s="18" t="n">
@@ -7810,92 +7977,92 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>2027/8/7</t>
+          <t>2027/8/5</t>
         </is>
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C61" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第4梯、企業專班：善首</t>
+          <t>暑期班、兒童夏令營 第4梯</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="18" t="inlineStr">
         <is>
-          <t>2027/8/8</t>
+          <t>2027/8/6</t>
         </is>
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C62" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>暑期班、彰化供佛齋僧大會、兒童夏令營 第5梯、企業專班：台中</t>
+          <t>暑期班、兒童夏令營 第4梯</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>2027/8/9</t>
+          <t>2027/8/7</t>
         </is>
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C63" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第5梯</t>
+          <t>暑期班、兒童夏令營 第4梯、企業專班：善首</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="18" t="inlineStr">
         <is>
-          <t>2027/8/10</t>
+          <t>2027/8/8</t>
         </is>
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第5梯</t>
+          <t>暑期班、彰化供佛齋僧大會、兒童夏令營 第5梯</t>
         </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>2027/8/11</t>
+          <t>2027/8/9</t>
         </is>
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C65" s="18" t="n">
@@ -7910,12 +8077,12 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>2027/8/12</t>
+          <t>2027/8/10</t>
         </is>
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C66" s="18" t="n">
@@ -7930,12 +8097,12 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="18" t="inlineStr">
         <is>
-          <t>2027/8/13</t>
+          <t>2027/8/11</t>
         </is>
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C67" s="18" t="n">
@@ -7950,12 +8117,12 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="18" t="inlineStr">
         <is>
-          <t>2027/9/18</t>
+          <t>2027/8/12</t>
         </is>
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C68" s="18" t="n">
@@ -7963,39 +8130,39 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>秋季班、一日禪（新加坡）</t>
+          <t>暑期班、兒童夏令營 第5梯</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="18" t="inlineStr">
         <is>
-          <t>2027/9/19</t>
+          <t>2027/8/13</t>
         </is>
       </c>
       <c r="B69" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C69" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>秋季班、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+          <t>暑期班、兒童夏令營 第5梯</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>2027/9/26</t>
+          <t>2027/8/14</t>
         </is>
       </c>
       <c r="B70" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C70" s="18" t="n">
@@ -8003,19 +8170,19 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）</t>
+          <t>兒童夏令營 第5梯、好好讀楞嚴（善覺）</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>2027/9/28</t>
+          <t>2027/8/15</t>
         </is>
       </c>
       <c r="B71" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C71" s="18" t="n">
@@ -8023,14 +8190,14 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>秋季班、教師禪修營</t>
+          <t>兒童夏令營 第6梯、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>2027/10/2</t>
+          <t>2027/9/18</t>
         </is>
       </c>
       <c r="B72" s="18" t="inlineStr">
@@ -8039,18 +8206,18 @@
         </is>
       </c>
       <c r="C72" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
+          <t>秋季班、一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="18" t="inlineStr">
         <is>
-          <t>2027/10/3</t>
+          <t>2027/9/19</t>
         </is>
       </c>
       <c r="B73" s="18" t="inlineStr">
@@ -8063,19 +8230,19 @@
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+          <t>秋季班、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
         </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="18" t="inlineStr">
         <is>
-          <t>2027/10/9</t>
+          <t>2027/9/26</t>
         </is>
       </c>
       <c r="B74" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C74" s="18" t="n">
@@ -8083,34 +8250,34 @@
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>秋季班、好好讀楞嚴（善覺）</t>
+          <t>秋季班、兒童哲學班（秋季）</t>
         </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="18" t="inlineStr">
         <is>
-          <t>2027/10/10</t>
+          <t>2027/9/28</t>
         </is>
       </c>
       <c r="B75" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C75" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
+          <t>秋季班、教師禪修營</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="18" t="inlineStr">
         <is>
-          <t>2027/10/16</t>
+          <t>2027/10/2</t>
         </is>
       </c>
       <c r="B76" s="18" t="inlineStr">
@@ -8119,18 +8286,18 @@
         </is>
       </c>
       <c r="C76" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>秋季班、一日禪（新加坡）</t>
+          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="18" t="inlineStr">
         <is>
-          <t>2027/10/17</t>
+          <t>2027/10/3</t>
         </is>
       </c>
       <c r="B77" s="18" t="inlineStr">
@@ -8139,23 +8306,23 @@
         </is>
       </c>
       <c r="C77" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="18" t="inlineStr">
         <is>
-          <t>2027/10/24</t>
+          <t>2027/10/9</t>
         </is>
       </c>
       <c r="B78" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C78" s="18" t="n">
@@ -8163,14 +8330,14 @@
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）</t>
+          <t>秋季班、好好讀楞嚴（善覺）</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="18" t="inlineStr">
         <is>
-          <t>2027/10/31</t>
+          <t>2027/10/10</t>
         </is>
       </c>
       <c r="B79" s="18" t="inlineStr">
@@ -8179,18 +8346,18 @@
         </is>
       </c>
       <c r="C79" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）</t>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="18" t="inlineStr">
         <is>
-          <t>2027/11/6</t>
+          <t>2027/10/16</t>
         </is>
       </c>
       <c r="B80" s="18" t="inlineStr">
@@ -8199,18 +8366,18 @@
         </is>
       </c>
       <c r="C80" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
+          <t>秋季班、一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="18" t="inlineStr">
         <is>
-          <t>2027/11/7</t>
+          <t>2027/10/17</t>
         </is>
       </c>
       <c r="B81" s="18" t="inlineStr">
@@ -8219,23 +8386,23 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+          <t>秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
         </is>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="18" t="inlineStr">
         <is>
-          <t>2027/11/13</t>
+          <t>2027/10/24</t>
         </is>
       </c>
       <c r="B82" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C82" s="18" t="n">
@@ -8243,14 +8410,14 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>秋季班、好好讀楞嚴（善覺）</t>
+          <t>秋季班、兒童哲學班（秋季）</t>
         </is>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="18" t="inlineStr">
         <is>
-          <t>2027/11/14</t>
+          <t>2027/10/31</t>
         </is>
       </c>
       <c r="B83" s="18" t="inlineStr">
@@ -8259,18 +8426,18 @@
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
+          <t>秋季班、兒童哲學班（秋季）</t>
         </is>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="18" t="inlineStr">
         <is>
-          <t>2027/11/20</t>
+          <t>2027/11/6</t>
         </is>
       </c>
       <c r="B84" s="18" t="inlineStr">
@@ -8279,18 +8446,18 @@
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>秋季班、一日禪（新加坡）</t>
+          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="18" t="inlineStr">
         <is>
-          <t>2027/11/21</t>
+          <t>2027/11/7</t>
         </is>
       </c>
       <c r="B85" s="18" t="inlineStr">
@@ -8299,23 +8466,23 @@
         </is>
       </c>
       <c r="C85" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
         </is>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="18" t="inlineStr">
         <is>
-          <t>2027/11/28</t>
+          <t>2027/11/13</t>
         </is>
       </c>
       <c r="B86" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C86" s="18" t="n">
@@ -8323,19 +8490,19 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）</t>
+          <t>秋季班、好好讀楞嚴（善覺）</t>
         </is>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="18" t="inlineStr">
         <is>
-          <t>2027/12/4</t>
+          <t>2027/11/14</t>
         </is>
       </c>
       <c r="B87" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C87" s="18" t="n">
@@ -8343,65 +8510,145 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="18" t="inlineStr">
         <is>
-          <t>2027/12/5</t>
+          <t>2027/11/20</t>
         </is>
       </c>
       <c r="B88" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C88" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+          <t>秋季班、一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="18" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>2027/11/21</t>
         </is>
       </c>
       <c r="B89" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C89" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>秋季班、好好讀楞嚴（善覺）</t>
+          <t>秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="18" t="inlineStr">
         <is>
+          <t>2027/11/28</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/4</t>
+        </is>
+      </c>
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/5</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/11</t>
+        </is>
+      </c>
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>秋季班、好好讀楞嚴（善覺）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="18" t="inlineStr">
+        <is>
           <t>2027/12/12</t>
         </is>
       </c>
-      <c r="B90" s="18" t="inlineStr">
+      <c r="B94" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C90" s="18" t="n">
+      <c r="C94" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D94" s="6" t="inlineStr">
         <is>
           <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
         </is>
@@ -8423,7 +8670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8596,9 +8843,233 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>本次個別調整明細</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>取消　好好讀楞嚴：板橋　3/13</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>3/13 三案重疊，以新加坡禪七為主</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>取消　英文一日禪（新加坡）　3/13</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>3/13 三案重疊，以新加坡禪七為主</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>改期　企業專班：台中　3/14 → 3/21</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>3/14 適逢新加坡禪七</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>取消　楞嚴經（新加坡）　3/21</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>合併至新加坡禪七</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>取消　英文一日禪（新加坡）　4/3</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>清明法會放蒙山（台中）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>改期　企業專班：台中　8/8 → 8/15</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>8/8 彰化供佛齋僧大會</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>加排　好好讀楞嚴：板橋　8/14</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂加排</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>加排　企業專班：台北　7/3</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>7 月場次補排</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>加排　企業專班：高雄　7/4</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>7 月場次補排</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>加排　好好讀楞嚴：板橋　7/10</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>7 月場次補排</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>加排　企業專班：台中　7/11</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>7 月場次補排</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>加排　企業專班：台北　9/4</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>9 月場次補排</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>加排　企業專班：高雄　9/5</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>9 月場次補排</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>加排　好好讀楞嚴：板橋　9/11</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>9 月場次補排</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>加排　企業專班：台中　9/12</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>9 月場次補排</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>時間　好好讀楞嚴：板橋　5/8</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>改為 14:00 上課</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>取消　八關齋戒暨共修法會　7/18</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>兒童夏令營 第2梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>拆分　浴佛節</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>5/8 浴佛節法會；5/9–5/16 浴佛週</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/行事曆/2027行事曆_華嚴海會更新版.xlsx
+++ b/行事曆/2027行事曆_華嚴海會更新版.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'活動總表'!$21:$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'活動總表'!$A$1:$G$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'見輝法師授課'!$14:$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'見輝法師授課'!$A$1:$E$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'見輝法師授課'!$A$1:$E$74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'活動重疊檢查'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'活動重疊檢查'!$A$1:$D$94</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'更新說明'!$A$1:$B$35</definedName>
@@ -1287,14 +1287,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="100.5" customHeight="1">
+    <row r="26" ht="87" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t>21（農2/14）
 新加坡禪七
 兒童哲學班（春季）
-八關齋戒暨共修法會
-企業專班：台中</t>
+八關齋戒暨共修法會</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -3877,12 +3876,12 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>共 10 堂</t>
+          <t>共 9 堂</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>2027/3/21、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/15、2027/9/12、2027/10/10、2027/11/14、2027/12/12　※ 3/14 改至 3/21（3/14 適逢新加坡禪七）；8/8 改至 8/15（8/8 彰化供佛齋僧大會）；7/11 加排（7 月場次補排）；9/12 加排（9 月場次補排）</t>
+          <t>2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/15、2027/9/12、2027/10/10、2027/11/14、2027/12/12　※ 3/14 取消（3 月適逢新加坡禪七（3/13–3/21），法師時間重疊）；8/8 改至 8/15（8/8 彰化供佛齋僧大會）；7/11 加排（7 月場次補排）；9/12 加排（9 月場次補排）</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -5233,7 +5232,7 @@
     <row r="55" ht="46" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>2027/3/21、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/15、2027/9/12、2027/10/10、2027/11/14、2027/12/12</t>
+          <t>2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/15、2027/9/12、2027/10/10、2027/11/14、2027/12/12</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -5263,7 +5262,7 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>每月第二個星期日；共 10 堂；3/14 改至 3/21（3/14 適逢新加坡禪七）；8/8 改至 8/15（8/8 彰化供佛齋僧大會）；7/11 加排（7 月場次補排）；9/12 加排（9 月場次補排）</t>
+          <t>每月第二個星期日；共 9 堂；3/14 取消（3 月適逢新加坡禪七（3/13–3/21），法師時間重疊）；8/8 改至 8/15（8/8 彰化供佛齋僧大會）；7/11 加排（7 月場次補排）；9/12 加排（9 月場次補排）</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5354,7 +5353,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>合計 52 堂；日期落在華嚴海會封鎖區間（12/13–12/26）者已取消。</t>
+          <t>合計 51 堂；日期落在華嚴海會封鎖區間（12/13–12/26）者已取消。</t>
         </is>
       </c>
     </row>
@@ -5464,12 +5463,12 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>10 堂</t>
+          <t>9 堂</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>2027/3/21、2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/15、2027/9/12、2027/10/10、2027/11/14、2027/12/12</t>
+          <t>2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/15、2027/9/12、2027/10/10、2027/11/14、2027/12/12</t>
         </is>
       </c>
     </row>
@@ -5657,49 +5656,49 @@
       </c>
       <c r="E17" s="6" t="inlineStr"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>2027/3/21</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台中</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="6" customHeight="1"/>
+    <row r="18" ht="6" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/3</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+    </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>2027/4/3</t>
+          <t>2027/4/4</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
@@ -5707,22 +5706,22 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>2027/4/4</t>
+          <t>2027/4/10</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
@@ -5730,22 +5729,22 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>2027/4/10</t>
+          <t>2027/4/11</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
@@ -5753,22 +5752,22 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>2027/4/11</t>
+          <t>2027/4/17</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
@@ -5776,69 +5775,69 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>2027/4/17</t>
+          <t>2027/4/18</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/1</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>一日禪（新加坡）</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>2027/4/18</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>楞嚴經（新加坡）</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="6" customHeight="1"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
+    </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>2027/5/1</t>
+          <t>2027/5/2</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
@@ -5846,22 +5845,22 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>2027/5/2</t>
+          <t>2027/5/8</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr"/>
@@ -5869,22 +5868,22 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>2027/5/8</t>
+          <t>2027/5/9</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
@@ -5892,22 +5891,22 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>2027/5/9</t>
+          <t>2027/5/15</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr"/>
@@ -5915,69 +5914,69 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>2027/5/15</t>
+          <t>2027/5/16</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="6" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>2027/6/5</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>一日禪（新加坡）</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>2027/5/16</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>楞嚴經（新加坡）</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33" ht="6" customHeight="1"/>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr"/>
+    </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>2027/6/5</t>
+          <t>2027/6/6</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr"/>
@@ -5985,22 +5984,22 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>2027/6/6</t>
+          <t>2027/6/12</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr"/>
@@ -6008,69 +6007,69 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>2027/6/12</t>
+          <t>2027/6/13</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="6" customHeight="1"/>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/3</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>好好讀楞嚴：板橋</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>善覺講堂</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>2027/6/13</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台中</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38" ht="6" customHeight="1"/>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr"/>
+    </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>2027/7/3</t>
+          <t>2027/7/4</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr"/>
@@ -6078,22 +6077,22 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>2027/7/4</t>
+          <t>2027/7/10</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr"/>
@@ -6101,22 +6100,22 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>2027/7/10</t>
+          <t>2027/7/11</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr"/>
@@ -6124,22 +6123,22 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>2027/7/11</t>
+          <t>2027/7/17</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr"/>
@@ -6147,17 +6146,17 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>2027/7/17</t>
+          <t>2027/7/18</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>一日禪（新加坡）</t>
+          <t>楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -6167,49 +6166,49 @@
       </c>
       <c r="E43" s="6" t="inlineStr"/>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t>2027/7/18</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
+    <row r="44" ht="6" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/1</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>星期日</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>楞嚴經（新加坡）</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr"/>
-    </row>
-    <row r="45" ht="6" customHeight="1"/>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：高雄</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>圓道禪寺（高雄）</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr"/>
+    </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>2027/8/1</t>
+          <t>2027/8/7</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>企業專班：台北</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善首講堂</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr"/>
@@ -6217,7 +6216,7 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>2027/8/7</t>
+          <t>2027/8/14</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
@@ -6227,12 +6226,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr"/>
@@ -6240,69 +6239,69 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>2027/8/14</t>
+          <t>2027/8/15</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49" ht="6" customHeight="1"/>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>2027/9/4</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>好好讀楞嚴：板橋</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>善覺講堂</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="18" t="inlineStr">
-        <is>
-          <t>2027/8/15</t>
-        </is>
-      </c>
-      <c r="B49" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台中</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr"/>
-    </row>
-    <row r="50" ht="6" customHeight="1"/>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr"/>
+    </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>2027/9/4</t>
+          <t>2027/9/5</t>
         </is>
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr"/>
@@ -6310,22 +6309,22 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>2027/9/5</t>
+          <t>2027/9/11</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr"/>
@@ -6333,22 +6332,22 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>2027/9/11</t>
+          <t>2027/9/12</t>
         </is>
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr"/>
@@ -6356,22 +6355,22 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>2027/9/12</t>
+          <t>2027/9/18</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr"/>
@@ -6379,69 +6378,69 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>2027/9/18</t>
+          <t>2027/9/19</t>
         </is>
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="6" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/2</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>一日禪（新加坡）</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="18" t="inlineStr">
-        <is>
-          <t>2027/9/19</t>
-        </is>
-      </c>
-      <c r="B56" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>楞嚴經（新加坡）</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr"/>
-    </row>
-    <row r="57" ht="6" customHeight="1"/>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr"/>
+    </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>2027/10/2</t>
+          <t>2027/10/3</t>
         </is>
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr"/>
@@ -6449,22 +6448,22 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>2027/10/3</t>
+          <t>2027/10/9</t>
         </is>
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr"/>
@@ -6472,22 +6471,22 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>2027/10/9</t>
+          <t>2027/10/10</t>
         </is>
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr"/>
@@ -6495,22 +6494,22 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>2027/10/10</t>
+          <t>2027/10/16</t>
         </is>
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr"/>
@@ -6518,69 +6517,69 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="18" t="inlineStr">
         <is>
-          <t>2027/10/16</t>
+          <t>2027/10/17</t>
         </is>
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63" ht="6" customHeight="1"/>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/6</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>一日禪（新加坡）</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="18" t="inlineStr">
-        <is>
-          <t>2027/10/17</t>
-        </is>
-      </c>
-      <c r="B63" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>楞嚴經（新加坡）</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64" ht="6" customHeight="1"/>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr"/>
+    </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>2027/11/6</t>
+          <t>2027/11/7</t>
         </is>
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr"/>
@@ -6588,22 +6587,22 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>2027/11/7</t>
+          <t>2027/11/13</t>
         </is>
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr"/>
@@ -6611,22 +6610,22 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="18" t="inlineStr">
         <is>
-          <t>2027/11/13</t>
+          <t>2027/11/14</t>
         </is>
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr"/>
@@ -6634,22 +6633,22 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="18" t="inlineStr">
         <is>
-          <t>2027/11/14</t>
+          <t>2027/11/20</t>
         </is>
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr"/>
@@ -6657,69 +6656,69 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="18" t="inlineStr">
         <is>
-          <t>2027/11/20</t>
+          <t>2027/11/21</t>
         </is>
       </c>
       <c r="B69" s="18" t="inlineStr">
         <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70" ht="6" customHeight="1"/>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/4</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>一日禪（新加坡）</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr"/>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="18" t="inlineStr">
-        <is>
-          <t>2027/11/21</t>
-        </is>
-      </c>
-      <c r="B70" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>楞嚴經（新加坡）</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr"/>
-    </row>
-    <row r="71" ht="6" customHeight="1"/>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr"/>
+    </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>2027/12/4</t>
+          <t>2027/12/5</t>
         </is>
       </c>
       <c r="B72" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr"/>
@@ -6727,22 +6726,22 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="18" t="inlineStr">
         <is>
-          <t>2027/12/5</t>
+          <t>2027/12/11</t>
         </is>
       </c>
       <c r="B73" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr"/>
@@ -6750,48 +6749,25 @@
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="18" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>2027/12/12</t>
         </is>
       </c>
       <c r="B74" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr"/>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="18" t="inlineStr">
-        <is>
-          <t>2027/12/12</t>
-        </is>
-      </c>
-      <c r="B75" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台中</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7026,11 +7002,11 @@
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>新加坡禪七、兒童哲學班（春季）、八關齋戒暨共修法會、企業專班：台中</t>
+          <t>新加坡禪七、兒童哲學班（春季）、八關齋戒暨共修法會</t>
         </is>
       </c>
     </row>
@@ -8877,12 +8853,12 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>改期　企業專班：台中　3/14 → 3/21</t>
+          <t>取消　企業專班：台中　3/14</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>3/14 適逢新加坡禪七</t>
+          <t>3 月適逢新加坡禪七（3/13–3/21），法師時間重疊</t>
         </is>
       </c>
     </row>

--- a/行事曆/2027行事曆_華嚴海會更新版.xlsx
+++ b/行事曆/2027行事曆_華嚴海會更新版.xlsx
@@ -18,10 +18,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'活動總表'!$21:$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'活動總表'!$A$1:$G$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'見輝法師授課'!$14:$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'見輝法師授課'!$A$1:$E$74</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'見輝法師授課'!$A$1:$E$71</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'活動重疊檢查'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'活動重疊檢查'!$A$1:$D$94</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'更新說明'!$A$1:$B$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'活動重疊檢查'!$A$1:$D$91</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'更新說明'!$A$1:$B$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1282,8 +1282,7 @@
       <c r="G25" s="6" t="inlineStr">
         <is>
           <t>20（農2/13）
-新加坡禪七
-一日禪（新加坡）</t>
+新加坡禪七</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2155,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
+    <row r="56" ht="46.5" customHeight="1">
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="5" t="n"/>
@@ -2175,17 +2174,15 @@
       <c r="G56" s="6" t="inlineStr">
         <is>
           <t>3（農5/29）
-夏安居禪七第二梯次
-企業專班：善首</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="60" customHeight="1">
+夏安居禪七第二梯次</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="46.5" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
           <t>4（農6/1）
-夏安居禪七第二梯次
-企業專班：高雄</t>
+夏安居禪七第二梯次</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -3834,12 +3831,12 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>共 10 堂</t>
+          <t>共 9 堂</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/7/3、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4　※ 7/3 加排（7 月場次補排）；9/4 加排（9 月場次補排）</t>
+          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4　※ 9/4 加排（9 月場次補排）</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -3855,12 +3852,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>共 10 堂</t>
+          <t>共 9 堂</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/7/4、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5　※ 7/4 加排（7 月場次補排）；9/5 加排（9 月場次補排）</t>
+          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5　※ 9/5 加排（9 月場次補排）</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -3960,12 +3957,12 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>共 7 堂</t>
+          <t>共 6 堂</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>2027/3/20、2027/4/17、2027/5/15、2027/7/17、2027/9/18、2027/10/16、2027/11/20　※ 12/18 取消（華嚴海會）</t>
+          <t>2027/4/17、2027/5/15、2027/7/17、2027/9/18、2027/10/16、2027/11/20　※ 3/20 取消（合併至新加坡禪七）；12/18 取消（華嚴海會）</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -5158,7 +5155,7 @@
     <row r="53" ht="46" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/7/3、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4</t>
+          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -5188,14 +5185,14 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>每月第一個星期六；共 10 堂；7/3 加排（7 月場次補排）；9/4 加排（9 月場次補排）</t>
+          <t>每月第一個星期六；共 9 堂；9/4 加排（9 月場次補排）</t>
         </is>
       </c>
     </row>
     <row r="54" ht="46" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/7/4、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5</t>
+          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -5225,7 +5222,7 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>每月第一個星期日；共 10 堂；7/4 加排（7 月場次補排）；9/5 加排（9 月場次補排）</t>
+          <t>每月第一個星期日；共 9 堂；9/5 加排（9 月場次補排）</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5353,7 +5350,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>合計 51 堂；日期落在華嚴海會封鎖區間（12/13–12/26）者已取消。</t>
+          <t>合計 48 堂；日期落在華嚴海會封鎖區間（12/13–12/26）者已取消。</t>
         </is>
       </c>
     </row>
@@ -5409,12 +5406,12 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>10 堂</t>
+          <t>9 堂</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/7/3、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4</t>
+          <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4</t>
         </is>
       </c>
     </row>
@@ -5436,12 +5433,12 @@
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>10 堂</t>
+          <t>9 堂</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/7/4、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5</t>
+          <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5514,12 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>7 堂</t>
+          <t>6 堂</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>2027/3/20、2027/4/17、2027/5/15、2027/7/17、2027/9/18、2027/10/16、2027/11/20　（取消：12/18）</t>
+          <t>2027/4/17、2027/5/15、2027/7/17、2027/9/18、2027/10/16、2027/11/20　（取消：12/18）</t>
         </is>
       </c>
     </row>
@@ -5633,49 +5630,49 @@
       </c>
       <c r="E16" s="6" t="inlineStr"/>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>2027/3/20</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
+    <row r="17" ht="6" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>2027/4/3</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>一日禪（新加坡）</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18" ht="6" customHeight="1"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr"/>
+    </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>2027/4/3</t>
+          <t>2027/4/4</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
@@ -5683,22 +5680,22 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>2027/4/4</t>
+          <t>2027/4/10</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
@@ -5706,22 +5703,22 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>2027/4/10</t>
+          <t>2027/4/11</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
@@ -5729,22 +5726,22 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>2027/4/11</t>
+          <t>2027/4/17</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
@@ -5752,69 +5749,69 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>2027/4/17</t>
+          <t>2027/4/18</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="6" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>2027/5/1</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>一日禪（新加坡）</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>2027/4/18</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>楞嚴經（新加坡）</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="6" customHeight="1"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+    </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>2027/5/1</t>
+          <t>2027/5/2</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
@@ -5822,22 +5819,22 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>2027/5/2</t>
+          <t>2027/5/8</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
@@ -5845,22 +5842,22 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>2027/5/8</t>
+          <t>2027/5/9</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr"/>
@@ -5868,22 +5865,22 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>2027/5/9</t>
+          <t>2027/5/15</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
@@ -5891,69 +5888,69 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>2027/5/15</t>
+          <t>2027/5/16</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>楞嚴經（新加坡）</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="6" customHeight="1"/>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>2027/6/5</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>一日禪（新加坡）</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>2027/5/16</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>楞嚴經（新加坡）</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>新加坡</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32" ht="6" customHeight="1"/>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台北</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>善首講堂</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr"/>
+    </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>2027/6/5</t>
+          <t>2027/6/6</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr"/>
@@ -5961,22 +5958,22 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>2027/6/6</t>
+          <t>2027/6/12</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>善覺講堂</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr"/>
@@ -5984,69 +5981,69 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>2027/6/12</t>
+          <t>2027/6/13</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>企業專班：台中</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="6" customHeight="1"/>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>2027/7/10</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
           <t>星期六</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>好好讀楞嚴：板橋</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>善覺講堂</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>2027/6/13</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台中</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37" ht="6" customHeight="1"/>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>2027/7/3</t>
+          <t>2027/7/11</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr"/>
@@ -6054,22 +6051,22 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>2027/7/4</t>
+          <t>2027/7/17</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr"/>
@@ -6077,68 +6074,46 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>2027/7/10</t>
+          <t>2027/7/18</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr"/>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>2027/7/11</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台中</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr"/>
-    </row>
+    <row r="41" ht="6" customHeight="1"/>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>2027/7/17</t>
+          <t>2027/8/1</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>一日禪（新加坡）</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>新加坡</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr"/>
@@ -6146,31 +6121,53 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>2027/7/18</t>
+          <t>2027/8/7</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>楞嚴經（新加坡）</t>
+          <t>企業專班：台北</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>新加坡</t>
+          <t>善首講堂</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr"/>
     </row>
-    <row r="44" ht="6" customHeight="1"/>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>2027/8/14</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr"/>
+    </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>2027/8/1</t>
+          <t>2027/8/15</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
@@ -6180,43 +6177,21 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr"/>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="18" t="inlineStr">
-        <is>
-          <t>2027/8/7</t>
-        </is>
-      </c>
-      <c r="B46" s="18" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台北</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>善首講堂</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr"/>
-    </row>
+    <row r="46" ht="6" customHeight="1"/>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>2027/8/14</t>
+          <t>2027/9/4</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
@@ -6226,12 +6201,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>企業專班：台北</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>善首講堂</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr"/>
@@ -6239,7 +6214,7 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>2027/8/15</t>
+          <t>2027/9/5</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
@@ -6249,36 +6224,58 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台中</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr"/>
     </row>
-    <row r="49" ht="6" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>2027/9/11</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr"/>
+    </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>2027/9/4</t>
+          <t>2027/9/12</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr"/>
@@ -6286,22 +6283,22 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>2027/9/5</t>
+          <t>2027/9/18</t>
         </is>
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr"/>
@@ -6309,53 +6306,31 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>2027/9/11</t>
+          <t>2027/9/19</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr"/>
     </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="18" t="inlineStr">
-        <is>
-          <t>2027/9/12</t>
-        </is>
-      </c>
-      <c r="B53" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台中</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr"/>
-    </row>
+    <row r="53" ht="6" customHeight="1"/>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>2027/9/18</t>
+          <t>2027/10/2</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
@@ -6365,12 +6340,12 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>一日禪（新加坡）</t>
+          <t>企業專班：台北</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>新加坡</t>
+          <t>善首講堂</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr"/>
@@ -6378,7 +6353,7 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>2027/9/19</t>
+          <t>2027/10/3</t>
         </is>
       </c>
       <c r="B55" s="18" t="inlineStr">
@@ -6388,36 +6363,58 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>楞嚴經（新加坡）</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>新加坡</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr"/>
     </row>
-    <row r="56" ht="6" customHeight="1"/>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>2027/10/9</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr"/>
+    </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>2027/10/2</t>
+          <t>2027/10/10</t>
         </is>
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr"/>
@@ -6425,22 +6422,22 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>2027/10/3</t>
+          <t>2027/10/16</t>
         </is>
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr"/>
@@ -6448,53 +6445,31 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>2027/10/9</t>
+          <t>2027/10/17</t>
         </is>
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr"/>
     </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="18" t="inlineStr">
-        <is>
-          <t>2027/10/10</t>
-        </is>
-      </c>
-      <c r="B60" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台中</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr"/>
-    </row>
+    <row r="60" ht="6" customHeight="1"/>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>2027/10/16</t>
+          <t>2027/11/6</t>
         </is>
       </c>
       <c r="B61" s="18" t="inlineStr">
@@ -6504,12 +6479,12 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>一日禪（新加坡）</t>
+          <t>企業專班：台北</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>新加坡</t>
+          <t>善首講堂</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr"/>
@@ -6517,7 +6492,7 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="18" t="inlineStr">
         <is>
-          <t>2027/10/17</t>
+          <t>2027/11/7</t>
         </is>
       </c>
       <c r="B62" s="18" t="inlineStr">
@@ -6527,36 +6502,58 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>楞嚴經（新加坡）</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>新加坡</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr"/>
     </row>
-    <row r="63" ht="6" customHeight="1"/>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>2027/11/13</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr"/>
+    </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="18" t="inlineStr">
         <is>
-          <t>2027/11/6</t>
+          <t>2027/11/14</t>
         </is>
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr"/>
@@ -6564,22 +6561,22 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>2027/11/7</t>
+          <t>2027/11/20</t>
         </is>
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>企業專班：高雄</t>
+          <t>一日禪（新加坡）</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>圓道禪寺（高雄）</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr"/>
@@ -6587,53 +6584,31 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>2027/11/13</t>
+          <t>2027/11/21</t>
         </is>
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴：板橋</t>
+          <t>楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr"/>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="18" t="inlineStr">
-        <is>
-          <t>2027/11/14</t>
-        </is>
-      </c>
-      <c r="B67" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台中</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr"/>
-    </row>
+    <row r="67" ht="6" customHeight="1"/>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="18" t="inlineStr">
         <is>
-          <t>2027/11/20</t>
+          <t>2027/12/4</t>
         </is>
       </c>
       <c r="B68" s="18" t="inlineStr">
@@ -6643,12 +6618,12 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>一日禪（新加坡）</t>
+          <t>企業專班：台北</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>新加坡</t>
+          <t>善首講堂</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr"/>
@@ -6656,7 +6631,7 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="18" t="inlineStr">
         <is>
-          <t>2027/11/21</t>
+          <t>2027/12/5</t>
         </is>
       </c>
       <c r="B69" s="18" t="inlineStr">
@@ -6666,108 +6641,61 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>楞嚴經（新加坡）</t>
+          <t>企業專班：高雄</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>新加坡</t>
+          <t>圓道禪寺（高雄）</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr"/>
     </row>
-    <row r="70" ht="6" customHeight="1"/>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>2027/12/11</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>好好讀楞嚴：板橋</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>善覺講堂</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr"/>
+    </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>2027/12/4</t>
+          <t>2027/12/12</t>
         </is>
       </c>
       <c r="B71" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>企業專班：台北</t>
+          <t>企業專班：台中</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>善首講堂</t>
+          <t>EPIC 禪藝實相人文空間（台中）</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr"/>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="18" t="inlineStr">
-        <is>
-          <t>2027/12/5</t>
-        </is>
-      </c>
-      <c r="B72" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：高雄</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>圓道禪寺（高雄）</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr"/>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="18" t="inlineStr">
-        <is>
-          <t>2027/12/11</t>
-        </is>
-      </c>
-      <c r="B73" s="18" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>好好讀楞嚴：板橋</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>善覺講堂</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr"/>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="18" t="inlineStr">
-        <is>
-          <t>2027/12/12</t>
-        </is>
-      </c>
-      <c r="B74" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>企業專班：台中</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>EPIC 禪藝實相人文空間（台中）</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6785,7 +6713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6973,107 +6901,107 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>2027/3/20</t>
+          <t>2027/3/21</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>新加坡禪七、一日禪（新加坡）</t>
+          <t>新加坡禪七、兒童哲學班（春季）、八關齋戒暨共修法會</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>2027/3/21</t>
+          <t>2027/4/3</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>新加坡禪七、兒童哲學班（春季）、八關齋戒暨共修法會</t>
+          <t>清明法會放蒙山（台中）、企業專班：善首</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>2027/4/3</t>
+          <t>2027/4/4</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（台中）、企業專班：善首</t>
+          <t>清明法會放蒙山（台北）、兒童哲學班（春季）、企業專班：高雄</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>2027/4/4</t>
+          <t>2027/4/10</t>
         </is>
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（台北）、兒童哲學班（春季）、企業專班：高雄</t>
+          <t>清明法會放蒙山（高雄）、好好讀楞嚴（善覺）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>2027/4/10</t>
+          <t>2027/4/11</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（高雄）、好好讀楞嚴（善覺）</t>
+          <t>清明法會放蒙山（板橋）、兒童哲學班（春季）、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>2027/4/11</t>
+          <t>2027/4/18</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
@@ -7082,23 +7010,23 @@
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（板橋）、兒童哲學班（春季）、企業專班：台中</t>
+          <t>兒童哲學班（春季）、楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>2027/4/18</t>
+          <t>2027/5/1</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
@@ -7106,99 +7034,99 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>兒童哲學班（春季）、楞嚴經（新加坡）</t>
+          <t>企業專班：善首、英文一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>2027/5/1</t>
+          <t>2027/5/2</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>企業專班：善首、英文一日禪（新加坡）</t>
+          <t>兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>2027/5/2</t>
+          <t>2027/5/8</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
+          <t>浴佛節法會、好好讀楞嚴（善覺） 14:00</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>2027/5/8</t>
+          <t>2027/5/9</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>浴佛節法會、好好讀楞嚴（善覺） 14:00</t>
+          <t>浴佛週、兒童哲學班（春季）、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>2027/5/9</t>
+          <t>2027/5/10</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>浴佛週、兒童哲學班（春季）、企業專班：台中</t>
+          <t>春季班、浴佛週</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>2027/5/10</t>
+          <t>2027/5/11</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
@@ -7213,12 +7141,12 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>2027/5/11</t>
+          <t>2027/5/12</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
@@ -7233,12 +7161,12 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>2027/5/12</t>
+          <t>2027/5/13</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
@@ -7253,12 +7181,12 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>2027/5/13</t>
+          <t>2027/5/14</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C26" s="18" t="n">
@@ -7273,12 +7201,12 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>2027/5/14</t>
+          <t>2027/5/15</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C27" s="18" t="n">
@@ -7286,74 +7214,74 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>春季班、浴佛週</t>
+          <t>浴佛週、一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>2027/5/15</t>
+          <t>2027/5/16</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>浴佛週、一日禪（新加坡）</t>
+          <t>浴佛週、兒童哲學班（春季）、楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>2027/5/16</t>
+          <t>2027/6/5</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>浴佛週、兒童哲學班（春季）、楞嚴經（新加坡）</t>
+          <t>企業專班：善首、英文一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>2027/6/5</t>
+          <t>2027/6/6</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>企業專班：善首、英文一日禪（新加坡）</t>
+          <t>兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>2027/6/6</t>
+          <t>2027/6/13</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
@@ -7362,18 +7290,18 @@
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
+          <t>兒童哲學班（春季）、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>2027/6/13</t>
+          <t>2027/6/20</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
@@ -7386,14 +7314,14 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>兒童哲學班（春季）、企業專班：台中</t>
+          <t>兒童哲學班（春季）、八關齋戒暨共修法會</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>2027/6/20</t>
+          <t>2027/7/11</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
@@ -7406,19 +7334,19 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>兒童哲學班（春季）、八關齋戒暨共修法會</t>
+          <t>兒童夏令營 第1梯、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>2027/7/3</t>
+          <t>2027/7/12</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C34" s="18" t="n">
@@ -7426,19 +7354,19 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>夏安居禪七第二梯次、企業專班：善首</t>
+          <t>暑期班、兒童夏令營 第1梯</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>2027/7/4</t>
+          <t>2027/7/13</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C35" s="18" t="n">
@@ -7446,19 +7374,19 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>夏安居禪七第二梯次、企業專班：高雄</t>
+          <t>暑期班、兒童夏令營 第1梯</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>2027/7/11</t>
+          <t>2027/7/14</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C36" s="18" t="n">
@@ -7466,19 +7394,19 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第1梯、企業專班：台中</t>
+          <t>暑期班、兒童夏令營 第1梯</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>2027/7/12</t>
+          <t>2027/7/15</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C37" s="18" t="n">
@@ -7493,12 +7421,12 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>2027/7/13</t>
+          <t>2027/7/16</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C38" s="18" t="n">
@@ -7513,52 +7441,52 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>2027/7/14</t>
+          <t>2027/7/17</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C39" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第1梯</t>
+          <t>暑期班、兒童夏令營 第1梯、一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>2027/7/15</t>
+          <t>2027/7/18</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第1梯</t>
+          <t>暑期班、兒童夏令營 第2梯、楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>2027/7/16</t>
+          <t>2027/7/19</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C41" s="18" t="n">
@@ -7566,59 +7494,59 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第1梯</t>
+          <t>暑期班、兒童夏令營 第2梯</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>2027/7/17</t>
+          <t>2027/7/20</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第1梯、一日禪（新加坡）</t>
+          <t>暑期班、兒童夏令營 第2梯</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>2027/7/18</t>
+          <t>2027/7/21</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C43" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第2梯、楞嚴經（新加坡）</t>
+          <t>暑期班、兒童夏令營 第2梯</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>2027/7/19</t>
+          <t>2027/7/22</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
@@ -7633,12 +7561,12 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>2027/7/20</t>
+          <t>2027/7/23</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
@@ -7653,12 +7581,12 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>2027/7/21</t>
+          <t>2027/7/24</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
@@ -7673,12 +7601,12 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>2027/7/22</t>
+          <t>2027/7/25</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
@@ -7686,19 +7614,19 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第2梯</t>
+          <t>暑期班、兒童夏令營 第3梯</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>2027/7/23</t>
+          <t>2027/7/26</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
@@ -7706,19 +7634,19 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第2梯</t>
+          <t>暑期班、兒童夏令營 第3梯</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>2027/7/24</t>
+          <t>2027/7/27</t>
         </is>
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C49" s="18" t="n">
@@ -7726,19 +7654,19 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第2梯</t>
+          <t>暑期班、兒童夏令營 第3梯</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>2027/7/25</t>
+          <t>2027/7/28</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C50" s="18" t="n">
@@ -7753,12 +7681,12 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>2027/7/26</t>
+          <t>2027/7/29</t>
         </is>
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
@@ -7773,12 +7701,12 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>2027/7/27</t>
+          <t>2027/7/30</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
@@ -7793,12 +7721,12 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>2027/7/28</t>
+          <t>2027/7/31</t>
         </is>
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C53" s="18" t="n">
@@ -7813,32 +7741,32 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>2027/7/29</t>
+          <t>2027/8/1</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第3梯</t>
+          <t>暑期班、兒童夏令營 第4梯、企業專班：高雄</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>2027/7/30</t>
+          <t>2027/8/2</t>
         </is>
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C55" s="18" t="n">
@@ -7846,19 +7774,19 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第3梯</t>
+          <t>暑期班、兒童夏令營 第4梯</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>2027/7/31</t>
+          <t>2027/8/3</t>
         </is>
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C56" s="18" t="n">
@@ -7866,39 +7794,39 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第3梯</t>
+          <t>暑期班、兒童夏令營 第4梯</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>2027/8/1</t>
+          <t>2027/8/4</t>
         </is>
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C57" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第4梯、企業專班：高雄</t>
+          <t>暑期班、兒童夏令營 第4梯</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>2027/8/2</t>
+          <t>2027/8/5</t>
         </is>
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C58" s="18" t="n">
@@ -7913,12 +7841,12 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>2027/8/3</t>
+          <t>2027/8/6</t>
         </is>
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C59" s="18" t="n">
@@ -7933,52 +7861,52 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>2027/8/4</t>
+          <t>2027/8/7</t>
         </is>
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C60" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第4梯</t>
+          <t>暑期班、兒童夏令營 第4梯、企業專班：善首</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>2027/8/5</t>
+          <t>2027/8/8</t>
         </is>
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C61" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第4梯</t>
+          <t>暑期班、彰化供佛齋僧大會、兒童夏令營 第5梯</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="18" t="inlineStr">
         <is>
-          <t>2027/8/6</t>
+          <t>2027/8/9</t>
         </is>
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="C62" s="18" t="n">
@@ -7986,59 +7914,59 @@
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第4梯</t>
+          <t>暑期班、兒童夏令營 第5梯</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>2027/8/7</t>
+          <t>2027/8/10</t>
         </is>
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C63" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第4梯、企業專班：善首</t>
+          <t>暑期班、兒童夏令營 第5梯</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="18" t="inlineStr">
         <is>
-          <t>2027/8/8</t>
+          <t>2027/8/11</t>
         </is>
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>暑期班、彰化供佛齋僧大會、兒童夏令營 第5梯</t>
+          <t>暑期班、兒童夏令營 第5梯</t>
         </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>2027/8/9</t>
+          <t>2027/8/12</t>
         </is>
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="C65" s="18" t="n">
@@ -8053,12 +7981,12 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>2027/8/10</t>
+          <t>2027/8/13</t>
         </is>
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期五</t>
         </is>
       </c>
       <c r="C66" s="18" t="n">
@@ -8073,12 +8001,12 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="18" t="inlineStr">
         <is>
-          <t>2027/8/11</t>
+          <t>2027/8/14</t>
         </is>
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C67" s="18" t="n">
@@ -8086,19 +8014,19 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第5梯</t>
+          <t>兒童夏令營 第5梯、好好讀楞嚴（善覺）</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="18" t="inlineStr">
         <is>
-          <t>2027/8/12</t>
+          <t>2027/8/15</t>
         </is>
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C68" s="18" t="n">
@@ -8106,19 +8034,19 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第5梯</t>
+          <t>兒童夏令營 第6梯、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="18" t="inlineStr">
         <is>
-          <t>2027/8/13</t>
+          <t>2027/9/18</t>
         </is>
       </c>
       <c r="B69" s="18" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C69" s="18" t="n">
@@ -8126,34 +8054,34 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第5梯</t>
+          <t>秋季班、一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>2027/8/14</t>
+          <t>2027/9/19</t>
         </is>
       </c>
       <c r="B70" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C70" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第5梯、好好讀楞嚴（善覺）</t>
+          <t>秋季班、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>2027/8/15</t>
+          <t>2027/9/26</t>
         </is>
       </c>
       <c r="B71" s="18" t="inlineStr">
@@ -8166,19 +8094,19 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第6梯、企業專班：台中</t>
+          <t>秋季班、兒童哲學班（秋季）</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>2027/9/18</t>
+          <t>2027/9/28</t>
         </is>
       </c>
       <c r="B72" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="C72" s="18" t="n">
@@ -8186,19 +8114,19 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>秋季班、一日禪（新加坡）</t>
+          <t>秋季班、教師禪修營</t>
         </is>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="18" t="inlineStr">
         <is>
-          <t>2027/9/19</t>
+          <t>2027/10/2</t>
         </is>
       </c>
       <c r="B73" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C73" s="18" t="n">
@@ -8206,14 +8134,14 @@
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>秋季班、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="18" t="inlineStr">
         <is>
-          <t>2027/9/26</t>
+          <t>2027/10/3</t>
         </is>
       </c>
       <c r="B74" s="18" t="inlineStr">
@@ -8222,23 +8150,23 @@
         </is>
       </c>
       <c r="C74" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）</t>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
         </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="18" t="inlineStr">
         <is>
-          <t>2027/9/28</t>
+          <t>2027/10/9</t>
         </is>
       </c>
       <c r="B75" s="18" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C75" s="18" t="n">
@@ -8246,19 +8174,19 @@
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>秋季班、教師禪修營</t>
+          <t>秋季班、好好讀楞嚴（善覺）</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="18" t="inlineStr">
         <is>
-          <t>2027/10/2</t>
+          <t>2027/10/10</t>
         </is>
       </c>
       <c r="B76" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C76" s="18" t="n">
@@ -8266,54 +8194,54 @@
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="18" t="inlineStr">
         <is>
-          <t>2027/10/3</t>
+          <t>2027/10/16</t>
         </is>
       </c>
       <c r="B77" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C77" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+          <t>秋季班、一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="18" t="inlineStr">
         <is>
-          <t>2027/10/9</t>
+          <t>2027/10/17</t>
         </is>
       </c>
       <c r="B78" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C78" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>秋季班、好好讀楞嚴（善覺）</t>
+          <t>秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="18" t="inlineStr">
         <is>
-          <t>2027/10/10</t>
+          <t>2027/10/24</t>
         </is>
       </c>
       <c r="B79" s="18" t="inlineStr">
@@ -8322,23 +8250,23 @@
         </is>
       </c>
       <c r="C79" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
+          <t>秋季班、兒童哲學班（秋季）</t>
         </is>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="18" t="inlineStr">
         <is>
-          <t>2027/10/16</t>
+          <t>2027/10/31</t>
         </is>
       </c>
       <c r="B80" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C80" s="18" t="n">
@@ -8346,34 +8274,34 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>秋季班、一日禪（新加坡）</t>
+          <t>秋季班、兒童哲學班（秋季）</t>
         </is>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="18" t="inlineStr">
         <is>
-          <t>2027/10/17</t>
+          <t>2027/11/6</t>
         </is>
       </c>
       <c r="B81" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="18" t="inlineStr">
         <is>
-          <t>2027/10/24</t>
+          <t>2027/11/7</t>
         </is>
       </c>
       <c r="B82" s="18" t="inlineStr">
@@ -8382,23 +8310,23 @@
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）</t>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
         </is>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="18" t="inlineStr">
         <is>
-          <t>2027/10/31</t>
+          <t>2027/11/13</t>
         </is>
       </c>
       <c r="B83" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C83" s="18" t="n">
@@ -8406,19 +8334,19 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）</t>
+          <t>秋季班、好好讀楞嚴（善覺）</t>
         </is>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="18" t="inlineStr">
         <is>
-          <t>2027/11/6</t>
+          <t>2027/11/14</t>
         </is>
       </c>
       <c r="B84" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C84" s="18" t="n">
@@ -8426,54 +8354,54 @@
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
         </is>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="18" t="inlineStr">
         <is>
-          <t>2027/11/7</t>
+          <t>2027/11/20</t>
         </is>
       </c>
       <c r="B85" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C85" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+          <t>秋季班、一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="18" t="inlineStr">
         <is>
-          <t>2027/11/13</t>
+          <t>2027/11/21</t>
         </is>
       </c>
       <c r="B86" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>秋季班、好好讀楞嚴（善覺）</t>
+          <t>秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
         </is>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="18" t="inlineStr">
         <is>
-          <t>2027/11/14</t>
+          <t>2027/11/28</t>
         </is>
       </c>
       <c r="B87" s="18" t="inlineStr">
@@ -8482,18 +8410,18 @@
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
+          <t>秋季班、兒童哲學班（秋季）</t>
         </is>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="18" t="inlineStr">
         <is>
-          <t>2027/11/20</t>
+          <t>2027/12/4</t>
         </is>
       </c>
       <c r="B88" s="18" t="inlineStr">
@@ -8502,18 +8430,18 @@
         </is>
       </c>
       <c r="C88" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>秋季班、一日禪（新加坡）</t>
+          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="18" t="inlineStr">
         <is>
-          <t>2027/11/21</t>
+          <t>2027/12/5</t>
         </is>
       </c>
       <c r="B89" s="18" t="inlineStr">
@@ -8522,23 +8450,23 @@
         </is>
       </c>
       <c r="C89" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、楞嚴經（新加坡）、八關齋戒暨共修法會</t>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="18" t="inlineStr">
         <is>
-          <t>2027/11/28</t>
+          <t>2027/12/11</t>
         </is>
       </c>
       <c r="B90" s="18" t="inlineStr">
         <is>
-          <t>星期日</t>
+          <t>星期六</t>
         </is>
       </c>
       <c r="C90" s="18" t="n">
@@ -8546,85 +8474,25 @@
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）</t>
+          <t>秋季班、好好讀楞嚴（善覺）</t>
         </is>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="18" t="inlineStr">
         <is>
-          <t>2027/12/4</t>
+          <t>2027/12/12</t>
         </is>
       </c>
       <c r="B91" s="18" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="C91" s="18" t="n">
         <v>3</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、企業專班：善首、英文一日禪（新加坡）</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="18" t="inlineStr">
-        <is>
-          <t>2027/12/5</t>
-        </is>
-      </c>
-      <c r="B92" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="18" t="inlineStr">
-        <is>
-          <t>2027/12/11</t>
-        </is>
-      </c>
-      <c r="B93" s="18" t="inlineStr">
-        <is>
-          <t>星期六</t>
-        </is>
-      </c>
-      <c r="C93" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>秋季班、好好讀楞嚴（善覺）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="18" t="inlineStr">
-        <is>
-          <t>2027/12/12</t>
-        </is>
-      </c>
-      <c r="B94" s="18" t="inlineStr">
-        <is>
-          <t>星期日</t>
-        </is>
-      </c>
-      <c r="C94" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
         <is>
           <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
         </is>
@@ -8646,7 +8514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8865,7 +8733,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>取消　楞嚴經（新加坡）　3/21</t>
+          <t>取消　一日禪（新加坡）　3/20</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -8877,55 +8745,55 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>取消　英文一日禪（新加坡）　4/3</t>
+          <t>取消　楞嚴經（新加坡）　3/21</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（台中）</t>
+          <t>合併至新加坡禪七</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>改期　企業專班：台中　8/8 → 8/15</t>
+          <t>取消　英文一日禪（新加坡）　4/3</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>8/8 彰化供佛齋僧大會</t>
+          <t>清明法會放蒙山（台中）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>加排　好好讀楞嚴：板橋　8/14</t>
+          <t>改期　企業專班：台中　8/8 → 8/15</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂加排</t>
+          <t>8/8 彰化供佛齋僧大會</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：台北　7/3</t>
+          <t>加排　好好讀楞嚴：板橋　8/14</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>7 月場次補排</t>
+          <t>善覺講堂加排</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：高雄　7/4</t>
+          <t>加排　好好讀楞嚴：板橋　7/10</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -8937,7 +8805,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>加排　好好讀楞嚴：板橋　7/10</t>
+          <t>加排　企業專班：台中　7/11</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -8949,19 +8817,19 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：台中　7/11</t>
+          <t>加排　企業專班：台北　9/4</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>7 月場次補排</t>
+          <t>9 月場次補排</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：台北　9/4</t>
+          <t>加排　企業專班：高雄　9/5</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -8973,7 +8841,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：高雄　9/5</t>
+          <t>加排　好好讀楞嚴：板橋　9/11</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -8985,7 +8853,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>加排　好好讀楞嚴：板橋　9/11</t>
+          <t>加排　企業專班：台中　9/12</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -8997,46 +8865,34 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：台中　9/12</t>
+          <t>時間　好好讀楞嚴：板橋　5/8</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>9 月場次補排</t>
+          <t>改為 14:00 上課</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>時間　好好讀楞嚴：板橋　5/8</t>
+          <t>取消　八關齋戒暨共修法會　7/18</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>改為 14:00 上課</t>
+          <t>兒童夏令營 第2梯</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>取消　八關齋戒暨共修法會　7/18</t>
+          <t>拆分　浴佛節</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>兒童夏令營 第2梯</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>拆分　浴佛節</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>5/8 浴佛節法會；5/9–5/16 浴佛週</t>
         </is>

--- a/行事曆/2027行事曆_華嚴海會更新版.xlsx
+++ b/行事曆/2027行事曆_華嚴海會更新版.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">'見輝法師授課'!$A$1:$E$71</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'活動重疊檢查'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'活動重疊檢查'!$A$1:$D$91</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'更新說明'!$A$1:$B$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'更新說明'!$A$1:$B$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1429,13 +1429,14 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="87" customHeight="1">
+    <row r="32" ht="114" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t>4（農2/28）
 清明法會放蒙山（台北）
 兒童哲學班（春季）
-企業專班：高雄</t>
+企業專班：高雄
+英文楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -2421,13 +2422,14 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
+    <row r="64" ht="87" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
           <t>1（農6/29）
 暑期班
 兒童夏令營 第4梯
-企業專班：高雄</t>
+企業專班：高雄
+英文楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -2470,7 +2472,8 @@
           <t>7（農7/6）
 暑期班
 兒童夏令營 第4梯
-企業專班：善首</t>
+企業專班：善首
+英文一日禪（新加坡）</t>
         </is>
       </c>
     </row>
@@ -2938,13 +2941,14 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="73.5" customHeight="1">
+    <row r="81" ht="100.5" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
           <t>3（農9/4）
 秋季班
 兒童哲學班（秋季）
-企業專班：高雄</t>
+企業專班：高雄
+英文楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -3224,13 +3228,14 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="73.5" customHeight="1">
+    <row r="90" ht="100.5" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
           <t>7（農10/10）
 秋季班
 兒童哲學班（秋季）
-企業專班：高雄</t>
+企業專班：高雄
+英文楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -3465,13 +3470,14 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="73.5" customHeight="1">
+    <row r="98" ht="100.5" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
           <t>5（農11/8）
 秋季班
 兒童哲學班（秋季）
-企業專班：高雄</t>
+企業專班：高雄
+英文楞嚴經（新加坡）</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -3752,7 +3758,7 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>2027/9/26、2027/10/3、2027/10/10、2027/10/17、2027/10/24、2027/10/31、2027/11/7、2027/11/14、2027/11/21、2027/11/28、2027/12/5、2027/12/12（原 14 堂，12/19、12/26 因華嚴海會取消）</t>
+          <t>2027/9/26、2027/10/3、2027/10/10、2027/10/17、2027/10/24、2027/10/31、2027/11/7、2027/11/14、2027/11/21、2027/11/28、2027/12/5、2027/12/12　※ 12/19 取消（華嚴海會）</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -3936,12 +3942,12 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>共 8 堂</t>
+          <t>共 7 堂</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>2027/3/14、2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/10/3、2027/11/7、2027/12/5</t>
+          <t>2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/10/3、2027/11/7、2027/12/5　※ 3/14 取消（合併至新加坡禪七）</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -4893,15 +4899,15 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="34" customHeight="1">
+    <row r="46" ht="46" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2027/9/26 起每週日</t>
+          <t>2027/9/26、2027/10/3、2027/10/10、2027/10/17、2027/10/24、2027/10/31、2027/11/7、2027/11/14、2027/11/21、2027/11/28、2027/12/5、2027/12/12</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>每週日</t>
+          <t>依各列日期</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -4926,7 +4932,7 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>共 12 堂（原 14 堂；12/19、12/26 因華嚴海會取消）；日期詳見上方課程場次表</t>
+          <t>每週日；2027/9/26–2027/12/19；共 12 堂；12/19 取消（華嚴海會）</t>
         </is>
       </c>
     </row>
@@ -6950,11 +6956,11 @@
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（台北）、兒童哲學班（春季）、企業專班：高雄</t>
+          <t>清明法會放蒙山（台北）、兒童哲學班（春季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
@@ -7750,11 +7756,11 @@
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第4梯、企業專班：高雄</t>
+          <t>暑期班、兒童夏令營 第4梯、企業專班：高雄、英文楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
@@ -7870,11 +7876,11 @@
         </is>
       </c>
       <c r="C60" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>暑期班、兒童夏令營 第4梯、企業專班：善首</t>
+          <t>暑期班、兒童夏令營 第4梯、企業專班：善首、英文一日禪（新加坡）</t>
         </is>
       </c>
     </row>
@@ -8150,11 +8156,11 @@
         </is>
       </c>
       <c r="C74" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
@@ -8310,11 +8316,11 @@
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
@@ -8450,11 +8456,11 @@
         </is>
       </c>
       <c r="C89" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄</t>
+          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
         </is>
       </c>
     </row>
@@ -8514,7 +8520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8745,7 +8751,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>取消　楞嚴經（新加坡）　3/21</t>
+          <t>取消　英文楞嚴經（新加坡）　3/14</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -8757,55 +8763,55 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>取消　英文一日禪（新加坡）　4/3</t>
+          <t>取消　楞嚴經（新加坡）　3/21</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（台中）</t>
+          <t>合併至新加坡禪七</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>改期　企業專班：台中　8/8 → 8/15</t>
+          <t>取消　英文一日禪（新加坡）　4/3</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>8/8 彰化供佛齋僧大會</t>
+          <t>清明法會放蒙山（台中）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>加排　好好讀楞嚴：板橋　8/14</t>
+          <t>改期　企業專班：台中　8/8 → 8/15</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂加排</t>
+          <t>8/8 彰化供佛齋僧大會</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>加排　好好讀楞嚴：板橋　7/10</t>
+          <t>加排　好好讀楞嚴：板橋　8/14</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>7 月場次補排</t>
+          <t>善覺講堂加排</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：台中　7/11</t>
+          <t>加排　好好讀楞嚴：板橋　7/10</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -8817,19 +8823,19 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：台北　9/4</t>
+          <t>加排　企業專班：台中　7/11</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>9 月場次補排</t>
+          <t>7 月場次補排</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：高雄　9/5</t>
+          <t>加排　企業專班：台北　9/4</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -8841,7 +8847,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>加排　好好讀楞嚴：板橋　9/11</t>
+          <t>加排　企業專班：高雄　9/5</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -8853,7 +8859,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：台中　9/12</t>
+          <t>加排　好好讀楞嚴：板橋　9/11</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -8865,34 +8871,46 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>時間　好好讀楞嚴：板橋　5/8</t>
+          <t>加排　企業專班：台中　9/12</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>改為 14:00 上課</t>
+          <t>9 月場次補排</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>取消　八關齋戒暨共修法會　7/18</t>
+          <t>時間　好好讀楞嚴：板橋　5/8</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第2梯</t>
+          <t>改為 14:00 上課</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="19" t="inlineStr">
         <is>
+          <t>取消　八關齋戒暨共修法會　7/18</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>兒童夏令營 第2梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
           <t>拆分　浴佛節</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>5/8 浴佛節法會；5/9–5/16 浴佛週</t>
         </is>

--- a/行事曆/2027行事曆_華嚴海會更新版.xlsx
+++ b/行事曆/2027行事曆_華嚴海會更新版.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2027行事曆" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="活動總表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="見輝法師授課" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="活動重疊檢查" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="更新說明" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027行事曆" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活動總表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="見輝法師授課" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活動重疊檢查" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'2027行事曆'!$A$1:$G$102</definedName>
@@ -21,7 +21,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">'見輝法師授課'!$A$1:$E$71</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'活動重疊檢查'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'活動重疊檢查'!$A$1:$D$91</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'更新說明'!$A$1:$B$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'更新說明'!$A$1:$B$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2044,8 +2044,8 @@
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>20（農5/16）
-兒童哲學班（春季）
-八關齋戒暨共修法會</t>
+八關齋戒暨共修法會
+兒童哲學班（春季） 成果展</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -3475,9 +3475,9 @@
         <is>
           <t>5（農11/8）
 秋季班
-兒童哲學班（秋季）
 企業專班：高雄
-英文楞嚴經（新加坡）</t>
+英文楞嚴經（新加坡）
+兒童哲學班（秋季） 成果展</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -3518,12 +3518,11 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="73.5" customHeight="1">
+    <row r="99" ht="46.5" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
           <t>12（農11/15）
 秋季班
-兒童哲學班（秋季）
 企業專班：台中</t>
         </is>
       </c>
@@ -3737,7 +3736,7 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>2027/3/7、2027/3/14、2027/3/21、2027/3/28、2027/4/4、2027/4/11、2027/4/18、2027/4/25、2027/5/2、2027/5/9、2027/5/16、2027/5/23、2027/5/30、2027/6/6、2027/6/13、2027/6/20</t>
+          <t>2027/3/7、2027/3/14、2027/3/21、2027/3/28、2027/4/4、2027/4/11、2027/4/18、2027/4/25、2027/5/2、2027/5/9、2027/5/16、2027/5/23、2027/5/30、2027/6/6、2027/6/13、2027/6/20　※ 6/20 成果展</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -3753,12 +3752,12 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>共 12 堂</t>
+          <t>共 11 堂</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>2027/9/26、2027/10/3、2027/10/10、2027/10/17、2027/10/24、2027/10/31、2027/11/7、2027/11/14、2027/11/21、2027/11/28、2027/12/5、2027/12/12　※ 12/19 取消（華嚴海會）</t>
+          <t>2027/9/26、2027/10/3、2027/10/10、2027/10/17、2027/10/24、2027/10/31、2027/11/7、2027/11/14、2027/11/21、2027/11/28、2027/12/5　※ 12/5 成果展</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -4862,15 +4861,15 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="34" customHeight="1">
+    <row r="45" ht="46" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2027/3/7 起每週日</t>
+          <t>2027/3/7、2027/3/14、2027/3/21、2027/3/28、2027/4/4、2027/4/11、2027/4/18、2027/4/25、2027/5/2、2027/5/9、2027/5/16、2027/5/23、2027/5/30、2027/6/6、2027/6/13、2027/6/20</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>每週日</t>
+          <t>依各列日期</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -4895,14 +4894,14 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>共 16 堂；日期詳見上方課程場次表</t>
+          <t>每週日；2027/3/7–2027/6/20；共 16 堂；6/20 成果展</t>
         </is>
       </c>
     </row>
     <row r="46" ht="46" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2027/9/26、2027/10/3、2027/10/10、2027/10/17、2027/10/24、2027/10/31、2027/11/7、2027/11/14、2027/11/21、2027/11/28、2027/12/5、2027/12/12</t>
+          <t>2027/9/26、2027/10/3、2027/10/10、2027/10/17、2027/10/24、2027/10/31、2027/11/7、2027/11/14、2027/11/21、2027/11/28、2027/12/5</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -4932,7 +4931,7 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>每週日；2027/9/26–2027/12/19；共 12 堂；12/19 取消（華嚴海會）</t>
+          <t>每週日；2027/9/26–2027/12/5；共 11 堂；12/5 成果展</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7319,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>兒童哲學班（春季）、八關齋戒暨共修法會</t>
+          <t>八關齋戒暨共修法會、兒童哲學班（春季） 成果展</t>
         </is>
       </c>
     </row>
@@ -8460,7 +8459,7 @@
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：高雄、英文楞嚴經（新加坡）</t>
+          <t>秋季班、企業專班：高雄、英文楞嚴經（新加坡）、兒童哲學班（秋季） 成果展</t>
         </is>
       </c>
     </row>
@@ -8496,11 +8495,11 @@
         </is>
       </c>
       <c r="C91" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>秋季班、兒童哲學班（秋季）、企業專班：台中</t>
+          <t>秋季班、企業專班：台中</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8653,69 +8652,69 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>秋季班原 9/13–12/24 共 15 週，12/13 起停課，實際上課 9/13–12/10 共 13 週；兒童哲學班（秋季）14 堂→12 堂（取消 12/19、12/26）；一日禪（新加坡）8 堂→7 堂（取消 12/18）；楞嚴經（新加坡）8 堂→7 堂（取消 12/19）。</t>
+          <t>秋季班原 9/13–12/24 共 15 週，12/13 起停課，實際上課 9/13–12/10 共 13 週；一日禪（新加坡）8 堂→7 堂（取消 12/18）；楞嚴經（新加坡）8 堂→7 堂（取消 12/19）。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>未受影響</t>
+          <t>兒童哲學班</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>好好讀楞嚴（善覺）12/11、企業專班：台中 12/12、兒童哲學班（秋季）12/12 均在封鎖區間之前，維持原排程。</t>
+          <t>依 2027 排程決議，週日班日期如下：春季 2027/3/7–2027/6/20 共 16 堂，6/20 成果展；秋季 2027/9/26–2027/12/5 共 11 堂，12/5 成果展。秋季原始 PDF 排至 12/26（14 堂），本版改以 12/5 結業，故 12/12 不再排課，12/19、12/26 亦已不在課程期間內。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>其他說明</t>
+          <t>未受影響</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>除上述異動外，其餘月份與活動內容均與原 2027 行事曆相同。</t>
+          <t>好好讀楞嚴（善覺）12/11、企業專班：台中 12/12 均在封鎖區間之前，維持原排程。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>其他說明</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>除上述異動外，其餘月份與活動內容均與原 2027 行事曆相同。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>製作日期</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>2026/10/07</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>本次個別調整明細</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>取消　好好讀楞嚴：板橋　3/13</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>3/13 三案重疊，以新加坡禪七為主</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>取消　英文一日禪（新加坡）　3/13</t>
+          <t>取消　好好讀楞嚴：板橋　3/13</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -8727,31 +8726,31 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>取消　企業專班：台中　3/14</t>
+          <t>取消　英文一日禪（新加坡）　3/13</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>3 月適逢新加坡禪七（3/13–3/21），法師時間重疊</t>
+          <t>3/13 三案重疊，以新加坡禪七為主</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>取消　一日禪（新加坡）　3/20</t>
+          <t>取消　企業專班：台中　3/14</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>合併至新加坡禪七</t>
+          <t>3 月適逢新加坡禪七（3/13–3/21），法師時間重疊</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>取消　英文楞嚴經（新加坡）　3/14</t>
+          <t>取消　一日禪（新加坡）　3/20</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -8763,7 +8762,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>取消　楞嚴經（新加坡）　3/21</t>
+          <t>取消　英文楞嚴經（新加坡）　3/14</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -8775,55 +8774,55 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>取消　英文一日禪（新加坡）　4/3</t>
+          <t>取消　楞嚴經（新加坡）　3/21</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>清明法會放蒙山（台中）</t>
+          <t>合併至新加坡禪七</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>改期　企業專班：台中　8/8 → 8/15</t>
+          <t>取消　英文一日禪（新加坡）　4/3</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>8/8 彰化供佛齋僧大會</t>
+          <t>清明法會放蒙山（台中）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>加排　好好讀楞嚴：板橋　8/14</t>
+          <t>改期　企業專班：台中　8/8 → 8/15</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>善覺講堂加排</t>
+          <t>8/8 彰化供佛齋僧大會</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>加排　好好讀楞嚴：板橋　7/10</t>
+          <t>加排　好好讀楞嚴：板橋　8/14</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>7 月場次補排</t>
+          <t>善覺講堂加排</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：台中　7/11</t>
+          <t>加排　好好讀楞嚴：板橋　7/10</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -8835,19 +8834,19 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：台北　9/4</t>
+          <t>加排　企業專班：台中　7/11</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>9 月場次補排</t>
+          <t>7 月場次補排</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：高雄　9/5</t>
+          <t>加排　企業專班：台北　9/4</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -8859,7 +8858,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>加排　好好讀楞嚴：板橋　9/11</t>
+          <t>加排　企業專班：高雄　9/5</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -8871,7 +8870,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>加排　企業專班：台中　9/12</t>
+          <t>加排　好好讀楞嚴：板橋　9/11</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -8883,34 +8882,70 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>時間　好好讀楞嚴：板橋　5/8</t>
+          <t>加排　企業專班：台中　9/12</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>改為 14:00 上課</t>
+          <t>9 月場次補排</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>取消　八關齋戒暨共修法會　7/18</t>
+          <t>時間　好好讀楞嚴：板橋　5/8</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>兒童夏令營 第2梯</t>
+          <t>改為 14:00 上課</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="19" t="inlineStr">
         <is>
+          <t>加註　兒童哲學班（春季）　6/20</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>該堂為成果展</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>加註　兒童哲學班（秋季）　12/5</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>該堂為成果展</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>取消　八關齋戒暨共修法會　7/18</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>兒童夏令營 第2梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
           <t>拆分　浴佛節</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>5/8 浴佛節法會；5/9–5/16 浴佛週</t>
         </is>
@@ -8918,8 +8953,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/行事曆/2027行事曆_華嚴海會更新版.xlsx
+++ b/行事曆/2027行事曆_華嚴海會更新版.xlsx
@@ -649,7 +649,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>每日顯示農曆日期；本版更新：華嚴海會 2027/12/15–2027/12/26（共 12 天），前置作業 2027/12/13–2027/12/14（共 2 天）；該期間原排定之其他活動均已取消。</t>
@@ -3681,11 +3681,11 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3723,7 +3723,7 @@
       <c r="F4" s="12" t="n"/>
       <c r="G4" s="13" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="33" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
           <t>兒童哲學班（春季）</t>
@@ -3744,7 +3744,7 @@
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="13" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="33" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
           <t>兒童哲學班（秋季）</t>
@@ -3870,7 +3870,7 @@
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="33" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
           <t>企業專班：台中</t>
@@ -3891,7 +3891,7 @@
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="13" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="33" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
           <t>好好讀楞嚴：板橋</t>
@@ -3912,7 +3912,7 @@
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="13" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="33" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
           <t>英文一日禪（新加坡）</t>
@@ -3996,7 +3996,7 @@
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="13" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="33" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
           <t>八關齋戒暨共修法會</t>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="46" customHeight="1">
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t>2027/1/1、2027/1/2、2027/1/3、2027/1/9、2027/1/10、2027/1/16、2027/1/17、2027/1/23、2027/1/24、2027/1/30、2027/1/31</t>
@@ -4787,7 +4787,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1">
+    <row r="43" ht="46.5" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>2027/12/15–2027/12/26</t>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="34" customHeight="1">
+    <row r="44" ht="73.5" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
           <t>2027/3/21、2027/6/20、2027/9/19、2027/10/17、2027/11/21</t>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="46" customHeight="1">
+    <row r="45" ht="73.5" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
           <t>2027/3/7、2027/3/14、2027/3/21、2027/3/28、2027/4/4、2027/4/11、2027/4/18、2027/4/25、2027/5/2、2027/5/9、2027/5/16、2027/5/23、2027/5/30、2027/6/6、2027/6/13、2027/6/20</t>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="46" customHeight="1">
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
           <t>2027/9/26、2027/10/3、2027/10/10、2027/10/17、2027/10/24、2027/10/31、2027/11/7、2027/11/14、2027/11/21、2027/11/28、2027/12/5</t>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="46" customHeight="1">
+    <row r="53" ht="46.5" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
           <t>2027/3/6、2027/4/3、2027/5/1、2027/6/5、2027/8/7、2027/9/4、2027/10/2、2027/11/6、2027/12/4</t>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="46" customHeight="1">
+    <row r="54" ht="46.5" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
           <t>2027/3/7、2027/4/4、2027/5/2、2027/6/6、2027/8/1、2027/9/5、2027/10/3、2027/11/7、2027/12/5</t>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="46" customHeight="1">
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
           <t>2027/4/11、2027/5/9、2027/6/13、2027/7/11、2027/8/15、2027/9/12、2027/10/10、2027/11/14、2027/12/12</t>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="46" customHeight="1">
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
           <t>2027/4/10、2027/5/8、2027/6/12、2027/7/10、2027/8/14、2027/9/11、2027/10/9、2027/11/13、2027/12/11</t>
@@ -5341,8 +5341,8 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -5393,7 +5393,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
+    <row r="6" ht="33" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
           <t>企業專班：台北</t>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
+    <row r="7" ht="33" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
           <t>企業專班：高雄</t>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
+    <row r="8" ht="33" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
           <t>企業專班：台中</t>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
+    <row r="9" ht="33" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
           <t>好好讀楞嚴：板橋</t>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
+    <row r="10" ht="33" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
           <t>一日禪（新加坡）</t>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
+    <row r="11" ht="33" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>楞嚴經（新加坡）</t>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr"/>
     </row>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21" ht="33" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
           <t>2027/4/11</t>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr"/>
     </row>
-    <row r="28" ht="20" customHeight="1">
+    <row r="28" ht="33" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
         <is>
           <t>2027/5/9</t>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr"/>
     </row>
-    <row r="35" ht="20" customHeight="1">
+    <row r="35" ht="33" customHeight="1">
       <c r="A35" s="18" t="inlineStr">
         <is>
           <t>2027/6/13</t>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr"/>
     </row>
-    <row r="38" ht="20" customHeight="1">
+    <row r="38" ht="33" customHeight="1">
       <c r="A38" s="18" t="inlineStr">
         <is>
           <t>2027/7/11</t>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr"/>
     </row>
-    <row r="45" ht="20" customHeight="1">
+    <row r="45" ht="33" customHeight="1">
       <c r="A45" s="18" t="inlineStr">
         <is>
           <t>2027/8/15</t>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr"/>
     </row>
-    <row r="50" ht="20" customHeight="1">
+    <row r="50" ht="33" customHeight="1">
       <c r="A50" s="18" t="inlineStr">
         <is>
           <t>2027/9/12</t>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr"/>
     </row>
-    <row r="57" ht="20" customHeight="1">
+    <row r="57" ht="33" customHeight="1">
       <c r="A57" s="18" t="inlineStr">
         <is>
           <t>2027/10/10</t>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr"/>
     </row>
-    <row r="64" ht="20" customHeight="1">
+    <row r="64" ht="33" customHeight="1">
       <c r="A64" s="18" t="inlineStr">
         <is>
           <t>2027/11/14</t>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr"/>
     </row>
-    <row r="71" ht="20" customHeight="1">
+    <row r="71" ht="33" customHeight="1">
       <c r="A71" s="18" t="inlineStr">
         <is>
           <t>2027/12/12</t>
@@ -6703,9 +6703,11 @@
       <c r="E71" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6724,7 +6726,7 @@
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="76" customWidth="1" min="4" max="4"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -8522,7 +8524,7 @@
   <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="96" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -8629,7 +8631,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="64" customHeight="1">
+    <row r="11" ht="76" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
         <is>
           <t>取消活動明細</t>
@@ -8656,7 +8658,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1">
+    <row r="13" ht="48" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
           <t>兒童哲學班</t>
